--- a/Figuras/UMAX_18-10-24/UMAX_18-10-24_sensibilidade.xlsx
+++ b/Figuras/UMAX_18-10-24/UMAX_18-10-24_sensibilidade.xlsx
@@ -425,101 +425,106 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T4"/>
+  <dimension ref="A1:U13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>Parametro variado</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>Preco Diesel [R$]</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Cotacao Dolar</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Preco Razao Elepot [USD]</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Preco R.E. Cor. Dolar [R$]</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Preco Bat [USD]</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Preco Bat Cor. Dolar [R$]</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Preco UC [USD]</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Preco UC Cor. Dolar [R$]</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>C-rate</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Nm,b</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Np,b</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Nm,uc</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Np,uc</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Volume Total [L]</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>Energia Total Bat. [kWh]</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>Energia Total UC. [kWh]</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>Energia Total [kWh]</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>Pth [kW]</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>VPL [R$]</t>
         </is>
@@ -529,186 +534,804 @@
       <c r="A2" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="B2" t="n">
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Preco Diesel</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
         <v>3.69</v>
       </c>
-      <c r="C2" t="n">
-        <v>5.57</v>
-      </c>
       <c r="D2" t="n">
-        <v>54.07994285714286</v>
+        <v>5.3</v>
       </c>
       <c r="E2" t="n">
-        <v>301.2252817142858</v>
+        <v>10</v>
       </c>
       <c r="F2" t="n">
-        <v>155.96</v>
+        <v>53</v>
       </c>
       <c r="G2" t="n">
-        <v>868.6972000000001</v>
+        <v>12.8</v>
       </c>
       <c r="H2" t="n">
-        <v>299.3875</v>
+        <v>67.84</v>
       </c>
       <c r="I2" t="n">
-        <v>1667.588375</v>
+        <v>9.75</v>
       </c>
       <c r="J2" t="n">
+        <v>51.675</v>
+      </c>
+      <c r="K2" t="n">
         <v>6</v>
       </c>
-      <c r="K2" t="n">
-        <v>20</v>
-      </c>
       <c r="L2" t="n">
-        <v>6</v>
+        <v>28</v>
       </c>
       <c r="M2" t="n">
         <v>5</v>
       </c>
       <c r="N2" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="O2" t="n">
-        <v>1382.4</v>
+        <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>245.76</v>
+        <v>1335.04</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.872</v>
+        <v>286.72</v>
       </c>
       <c r="R2" t="n">
-        <v>247.632</v>
+        <v>0</v>
       </c>
       <c r="S2" t="n">
+        <v>286.72</v>
+      </c>
+      <c r="T2" t="n">
         <v>1550</v>
       </c>
-      <c r="T2" t="n">
-        <v>3661149.655682893</v>
+      <c r="U2" t="n">
+        <v>4461322.518970323</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="B3" t="n">
-        <v>5.78</v>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Preco Diesel</t>
+        </is>
       </c>
       <c r="C3" t="n">
-        <v>5.57</v>
+        <v>7.46</v>
       </c>
       <c r="D3" t="n">
-        <v>54.07994285714286</v>
+        <v>5.3</v>
       </c>
       <c r="E3" t="n">
-        <v>301.2252817142858</v>
+        <v>10</v>
       </c>
       <c r="F3" t="n">
-        <v>155.96</v>
+        <v>53</v>
       </c>
       <c r="G3" t="n">
-        <v>868.6972000000001</v>
+        <v>12.8</v>
       </c>
       <c r="H3" t="n">
-        <v>299.3875</v>
+        <v>67.84</v>
       </c>
       <c r="I3" t="n">
-        <v>1667.588375</v>
+        <v>9.75</v>
       </c>
       <c r="J3" t="n">
+        <v>51.675</v>
+      </c>
+      <c r="K3" t="n">
         <v>6</v>
       </c>
-      <c r="K3" t="n">
-        <v>18</v>
-      </c>
       <c r="L3" t="n">
-        <v>7</v>
+        <v>28</v>
       </c>
       <c r="M3" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="N3" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="O3" t="n">
-        <v>1392</v>
+        <v>1</v>
       </c>
       <c r="P3" t="n">
-        <v>258.048</v>
+        <v>1179.136</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.4976</v>
+        <v>229.376</v>
       </c>
       <c r="R3" t="n">
-        <v>259.5456</v>
+        <v>0.8735999999999999</v>
       </c>
       <c r="S3" t="n">
-        <v>1575</v>
+        <v>230.2496</v>
       </c>
       <c r="T3" t="n">
-        <v>7476206.679312889</v>
+        <v>1450</v>
+      </c>
+      <c r="U3" t="n">
+        <v>9329164.31224378</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="B4" t="n">
-        <v>7.46</v>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Cotacao Dolar</t>
+        </is>
       </c>
       <c r="C4" t="n">
-        <v>5.57</v>
+        <v>5.78</v>
       </c>
       <c r="D4" t="n">
-        <v>54.07994285714286</v>
+        <v>4.58</v>
       </c>
       <c r="E4" t="n">
-        <v>301.2252817142858</v>
+        <v>10</v>
       </c>
       <c r="F4" t="n">
-        <v>155.96</v>
+        <v>45.8</v>
       </c>
       <c r="G4" t="n">
-        <v>868.6972000000001</v>
+        <v>12.8</v>
       </c>
       <c r="H4" t="n">
-        <v>299.3875</v>
+        <v>58.624</v>
       </c>
       <c r="I4" t="n">
-        <v>1667.588375</v>
+        <v>9.75</v>
       </c>
       <c r="J4" t="n">
+        <v>44.655</v>
+      </c>
+      <c r="K4" t="n">
         <v>6</v>
       </c>
-      <c r="K4" t="n">
+      <c r="L4" t="n">
+        <v>28</v>
+      </c>
+      <c r="M4" t="n">
+        <v>4</v>
+      </c>
+      <c r="N4" t="n">
+        <v>27</v>
+      </c>
+      <c r="O4" t="n">
+        <v>1</v>
+      </c>
+      <c r="P4" t="n">
+        <v>1282.304</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>229.376</v>
+      </c>
+      <c r="R4" t="n">
+        <v>1.6848</v>
+      </c>
+      <c r="S4" t="n">
+        <v>231.0608</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1375</v>
+      </c>
+      <c r="U4" t="n">
+        <v>7088314.035541581</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Cotacao Dolar</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>5.78</v>
+      </c>
+      <c r="D5" t="n">
+        <v>6.31</v>
+      </c>
+      <c r="E5" t="n">
+        <v>10</v>
+      </c>
+      <c r="F5" t="n">
+        <v>63.09999999999999</v>
+      </c>
+      <c r="G5" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="H5" t="n">
+        <v>80.768</v>
+      </c>
+      <c r="I5" t="n">
+        <v>9.75</v>
+      </c>
+      <c r="J5" t="n">
+        <v>61.52249999999999</v>
+      </c>
+      <c r="K5" t="n">
+        <v>6</v>
+      </c>
+      <c r="L5" t="n">
+        <v>27</v>
+      </c>
+      <c r="M5" t="n">
+        <v>5</v>
+      </c>
+      <c r="N5" t="n">
         <v>13</v>
       </c>
-      <c r="L4" t="n">
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>1287.36</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>276.48</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="n">
+        <v>276.48</v>
+      </c>
+      <c r="T5" t="n">
+        <v>1175</v>
+      </c>
+      <c r="U5" t="n">
+        <v>7362142.627864531</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Preco Razao Elepot</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>5.78</v>
+      </c>
+      <c r="D6" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="E6" t="n">
+        <v>5</v>
+      </c>
+      <c r="F6" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="G6" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="H6" t="n">
+        <v>67.84</v>
+      </c>
+      <c r="I6" t="n">
+        <v>9.75</v>
+      </c>
+      <c r="J6" t="n">
+        <v>51.675</v>
+      </c>
+      <c r="K6" t="n">
+        <v>6</v>
+      </c>
+      <c r="L6" t="n">
+        <v>27</v>
+      </c>
+      <c r="M6" t="n">
+        <v>4</v>
+      </c>
+      <c r="N6" t="n">
+        <v>30</v>
+      </c>
+      <c r="O6" t="n">
+        <v>1</v>
+      </c>
+      <c r="P6" t="n">
+        <v>1267.968</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>221.184</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1.872</v>
+      </c>
+      <c r="S6" t="n">
+        <v>223.056</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1275</v>
+      </c>
+      <c r="U6" t="n">
+        <v>6834077.596661252</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Preco Razao Elepot</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>5.78</v>
+      </c>
+      <c r="D7" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="E7" t="n">
+        <v>20</v>
+      </c>
+      <c r="F7" t="n">
+        <v>106</v>
+      </c>
+      <c r="G7" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="H7" t="n">
+        <v>67.84</v>
+      </c>
+      <c r="I7" t="n">
+        <v>9.75</v>
+      </c>
+      <c r="J7" t="n">
+        <v>51.675</v>
+      </c>
+      <c r="K7" t="n">
+        <v>6</v>
+      </c>
+      <c r="L7" t="n">
+        <v>27</v>
+      </c>
+      <c r="M7" t="n">
+        <v>4</v>
+      </c>
+      <c r="N7" t="n">
+        <v>30</v>
+      </c>
+      <c r="O7" t="n">
+        <v>1</v>
+      </c>
+      <c r="P7" t="n">
+        <v>1267.968</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>221.184</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1.872</v>
+      </c>
+      <c r="S7" t="n">
+        <v>223.056</v>
+      </c>
+      <c r="T7" t="n">
+        <v>1275</v>
+      </c>
+      <c r="U7" t="n">
+        <v>6675077.596661254</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Preco Bat</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>5.78</v>
+      </c>
+      <c r="D8" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="E8" t="n">
         <v>10</v>
       </c>
-      <c r="M4" t="n">
+      <c r="F8" t="n">
+        <v>53</v>
+      </c>
+      <c r="G8" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="H8" t="n">
+        <v>33.92</v>
+      </c>
+      <c r="I8" t="n">
+        <v>9.75</v>
+      </c>
+      <c r="J8" t="n">
+        <v>51.675</v>
+      </c>
+      <c r="K8" t="n">
+        <v>6</v>
+      </c>
+      <c r="L8" t="n">
+        <v>27</v>
+      </c>
+      <c r="M8" t="n">
+        <v>5</v>
+      </c>
+      <c r="N8" t="n">
+        <v>14</v>
+      </c>
+      <c r="O8" t="n">
+        <v>1</v>
+      </c>
+      <c r="P8" t="n">
+        <v>1398.464</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>276.48</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0.8735999999999999</v>
+      </c>
+      <c r="S8" t="n">
+        <v>277.3536</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1550</v>
+      </c>
+      <c r="U8" t="n">
+        <v>7898646.925555612</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Preco Bat</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>5.78</v>
+      </c>
+      <c r="D9" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="E9" t="n">
+        <v>10</v>
+      </c>
+      <c r="F9" t="n">
+        <v>53</v>
+      </c>
+      <c r="G9" t="n">
+        <v>34.688</v>
+      </c>
+      <c r="H9" t="n">
+        <v>183.8464</v>
+      </c>
+      <c r="I9" t="n">
+        <v>9.75</v>
+      </c>
+      <c r="J9" t="n">
+        <v>51.675</v>
+      </c>
+      <c r="K9" t="n">
+        <v>6</v>
+      </c>
+      <c r="L9" t="n">
+        <v>27</v>
+      </c>
+      <c r="M9" t="n">
+        <v>5</v>
+      </c>
+      <c r="N9" t="n">
+        <v>17</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>1287.36</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>276.48</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" t="n">
+        <v>276.48</v>
+      </c>
+      <c r="T9" t="n">
+        <v>1575</v>
+      </c>
+      <c r="U9" t="n">
+        <v>5924488.802757631</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Preco UC</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>5.78</v>
+      </c>
+      <c r="D10" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="E10" t="n">
+        <v>10</v>
+      </c>
+      <c r="F10" t="n">
+        <v>53</v>
+      </c>
+      <c r="G10" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="H10" t="n">
+        <v>67.84</v>
+      </c>
+      <c r="I10" t="n">
+        <v>5.85</v>
+      </c>
+      <c r="J10" t="n">
+        <v>31.005</v>
+      </c>
+      <c r="K10" t="n">
+        <v>6</v>
+      </c>
+      <c r="L10" t="n">
+        <v>27</v>
+      </c>
+      <c r="M10" t="n">
+        <v>4</v>
+      </c>
+      <c r="N10" t="n">
+        <v>30</v>
+      </c>
+      <c r="O10" t="n">
+        <v>1</v>
+      </c>
+      <c r="P10" t="n">
+        <v>1267.968</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>221.184</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.872</v>
+      </c>
+      <c r="S10" t="n">
+        <v>223.056</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1275</v>
+      </c>
+      <c r="U10" t="n">
+        <v>6790999.196661252</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Preco UC</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>5.78</v>
+      </c>
+      <c r="D11" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="E11" t="n">
+        <v>10</v>
+      </c>
+      <c r="F11" t="n">
+        <v>53</v>
+      </c>
+      <c r="G11" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="H11" t="n">
+        <v>67.84</v>
+      </c>
+      <c r="I11" t="n">
+        <v>13.65</v>
+      </c>
+      <c r="J11" t="n">
+        <v>72.345</v>
+      </c>
+      <c r="K11" t="n">
+        <v>6</v>
+      </c>
+      <c r="L11" t="n">
+        <v>28</v>
+      </c>
+      <c r="M11" t="n">
+        <v>5</v>
+      </c>
+      <c r="N11" t="n">
+        <v>14</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>1335.04</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>286.72</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" t="n">
+        <v>286.72</v>
+      </c>
+      <c r="T11" t="n">
+        <v>1550</v>
+      </c>
+      <c r="U11" t="n">
+        <v>7607744.206532921</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>C-rate</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>5.78</v>
+      </c>
+      <c r="D12" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="E12" t="n">
+        <v>10</v>
+      </c>
+      <c r="F12" t="n">
+        <v>53</v>
+      </c>
+      <c r="G12" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="H12" t="n">
+        <v>67.84</v>
+      </c>
+      <c r="I12" t="n">
+        <v>9.75</v>
+      </c>
+      <c r="J12" t="n">
+        <v>51.675</v>
+      </c>
+      <c r="K12" t="n">
         <v>2</v>
       </c>
-      <c r="N4" t="n">
+      <c r="L12" t="n">
+        <v>26</v>
+      </c>
+      <c r="M12" t="n">
+        <v>4</v>
+      </c>
+      <c r="N12" t="n">
+        <v>26</v>
+      </c>
+      <c r="O12" t="n">
+        <v>2</v>
+      </c>
+      <c r="P12" t="n">
+        <v>1404.416</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>212.992</v>
+      </c>
+      <c r="R12" t="n">
+        <v>3.2448</v>
+      </c>
+      <c r="S12" t="n">
+        <v>216.2368</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1025</v>
+      </c>
+      <c r="U12" t="n">
+        <v>2601760.656935178</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>C-rate</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>5.78</v>
+      </c>
+      <c r="D13" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="E13" t="n">
         <v>10</v>
       </c>
-      <c r="O4" t="n">
-        <v>1398.4</v>
-      </c>
-      <c r="P4" t="n">
-        <v>266.24</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>1.248</v>
-      </c>
-      <c r="R4" t="n">
-        <v>267.488</v>
-      </c>
-      <c r="S4" t="n">
-        <v>1600</v>
-      </c>
-      <c r="T4" t="n">
-        <v>10552870.89172375</v>
+      <c r="F13" t="n">
+        <v>53</v>
+      </c>
+      <c r="G13" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="H13" t="n">
+        <v>67.84</v>
+      </c>
+      <c r="I13" t="n">
+        <v>9.75</v>
+      </c>
+      <c r="J13" t="n">
+        <v>51.675</v>
+      </c>
+      <c r="K13" t="n">
+        <v>10</v>
+      </c>
+      <c r="L13" t="n">
+        <v>28</v>
+      </c>
+      <c r="M13" t="n">
+        <v>3</v>
+      </c>
+      <c r="N13" t="n">
+        <v>14</v>
+      </c>
+      <c r="O13" t="n">
+        <v>1</v>
+      </c>
+      <c r="P13" t="n">
+        <v>912.128</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>172.032</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0.8735999999999999</v>
+      </c>
+      <c r="S13" t="n">
+        <v>172.9056</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1950</v>
+      </c>
+      <c r="U13" t="n">
+        <v>7786784.045848669</v>
       </c>
     </row>
   </sheetData>

--- a/Figuras/UMAX_18-10-24/UMAX_18-10-24_sensibilidade.xlsx
+++ b/Figuras/UMAX_18-10-24/UMAX_18-10-24_sensibilidade.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U13"/>
+  <dimension ref="A1:W17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -481,50 +481,60 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
+          <t>Nm_b min</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Nm_uc min</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
           <t>Nm,b</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Np,b</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Nm,uc</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>Np,uc</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>Volume Total [L]</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>Energia Total Bat. [kWh]</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>Energia Total UC. [kWh]</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>Energia Total [kWh]</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>Pth [kW]</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>VPL [R$]</t>
         </is>
@@ -567,33 +577,39 @@
         <v>6</v>
       </c>
       <c r="L2" t="n">
+        <v>15</v>
+      </c>
+      <c r="M2" t="n">
+        <v>11</v>
+      </c>
+      <c r="N2" t="n">
         <v>28</v>
       </c>
-      <c r="M2" t="n">
+      <c r="O2" t="n">
         <v>5</v>
       </c>
-      <c r="N2" t="n">
+      <c r="P2" t="n">
         <v>12</v>
       </c>
-      <c r="O2" t="n">
+      <c r="Q2" t="n">
         <v>0</v>
       </c>
-      <c r="P2" t="n">
+      <c r="R2" t="n">
         <v>1335.04</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>286.72</v>
-      </c>
-      <c r="R2" t="n">
-        <v>0</v>
       </c>
       <c r="S2" t="n">
         <v>286.72</v>
       </c>
       <c r="T2" t="n">
-        <v>1550</v>
+        <v>0</v>
       </c>
       <c r="U2" t="n">
+        <v>286.72</v>
+      </c>
+      <c r="V2" t="n">
+        <v>1150</v>
+      </c>
+      <c r="W2" t="n">
         <v>4461322.518970323</v>
       </c>
     </row>
@@ -634,34 +650,40 @@
         <v>6</v>
       </c>
       <c r="L3" t="n">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="M3" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="N3" t="n">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="O3" t="n">
+        <v>5</v>
+      </c>
+      <c r="P3" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q3" t="n">
         <v>1</v>
       </c>
-      <c r="P3" t="n">
-        <v>1179.136</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>229.376</v>
-      </c>
       <c r="R3" t="n">
-        <v>0.8735999999999999</v>
+        <v>1390.528</v>
       </c>
       <c r="S3" t="n">
-        <v>230.2496</v>
+        <v>276.48</v>
       </c>
       <c r="T3" t="n">
-        <v>1450</v>
+        <v>0.8111999999999999</v>
       </c>
       <c r="U3" t="n">
-        <v>9329164.31224378</v>
+        <v>277.2912</v>
+      </c>
+      <c r="V3" t="n">
+        <v>1400</v>
+      </c>
+      <c r="W3" t="n">
+        <v>9466060.856189825</v>
       </c>
     </row>
     <row r="4">
@@ -701,34 +723,40 @@
         <v>6</v>
       </c>
       <c r="L4" t="n">
+        <v>15</v>
+      </c>
+      <c r="M4" t="n">
+        <v>11</v>
+      </c>
+      <c r="N4" t="n">
         <v>28</v>
       </c>
-      <c r="M4" t="n">
+      <c r="O4" t="n">
         <v>4</v>
       </c>
-      <c r="N4" t="n">
-        <v>27</v>
-      </c>
-      <c r="O4" t="n">
+      <c r="P4" t="n">
+        <v>21</v>
+      </c>
+      <c r="Q4" t="n">
         <v>1</v>
       </c>
-      <c r="P4" t="n">
-        <v>1282.304</v>
-      </c>
-      <c r="Q4" t="n">
+      <c r="R4" t="n">
+        <v>1234.688</v>
+      </c>
+      <c r="S4" t="n">
         <v>229.376</v>
       </c>
-      <c r="R4" t="n">
-        <v>1.6848</v>
-      </c>
-      <c r="S4" t="n">
-        <v>231.0608</v>
-      </c>
       <c r="T4" t="n">
+        <v>1.3104</v>
+      </c>
+      <c r="U4" t="n">
+        <v>230.6864</v>
+      </c>
+      <c r="V4" t="n">
         <v>1375</v>
       </c>
-      <c r="U4" t="n">
-        <v>7088314.035541581</v>
+      <c r="W4" t="n">
+        <v>7143157.39965963</v>
       </c>
     </row>
     <row r="5">
@@ -768,34 +796,40 @@
         <v>6</v>
       </c>
       <c r="L5" t="n">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="M5" t="n">
+        <v>11</v>
+      </c>
+      <c r="N5" t="n">
+        <v>28</v>
+      </c>
+      <c r="O5" t="n">
         <v>5</v>
       </c>
-      <c r="N5" t="n">
+      <c r="P5" t="n">
         <v>13</v>
       </c>
-      <c r="O5" t="n">
+      <c r="Q5" t="n">
         <v>0</v>
       </c>
-      <c r="P5" t="n">
-        <v>1287.36</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>276.48</v>
-      </c>
       <c r="R5" t="n">
+        <v>1335.04</v>
+      </c>
+      <c r="S5" t="n">
+        <v>286.72</v>
+      </c>
+      <c r="T5" t="n">
         <v>0</v>
       </c>
-      <c r="S5" t="n">
-        <v>276.48</v>
-      </c>
-      <c r="T5" t="n">
-        <v>1175</v>
-      </c>
       <c r="U5" t="n">
-        <v>7362142.627864531</v>
+        <v>286.72</v>
+      </c>
+      <c r="V5" t="n">
+        <v>1225</v>
+      </c>
+      <c r="W5" t="n">
+        <v>7399294.871687513</v>
       </c>
     </row>
     <row r="6">
@@ -835,34 +869,40 @@
         <v>6</v>
       </c>
       <c r="L6" t="n">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="M6" t="n">
+        <v>11</v>
+      </c>
+      <c r="N6" t="n">
+        <v>28</v>
+      </c>
+      <c r="O6" t="n">
         <v>4</v>
       </c>
-      <c r="N6" t="n">
-        <v>30</v>
-      </c>
-      <c r="O6" t="n">
+      <c r="P6" t="n">
+        <v>24</v>
+      </c>
+      <c r="Q6" t="n">
         <v>1</v>
       </c>
-      <c r="P6" t="n">
-        <v>1267.968</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>221.184</v>
-      </c>
       <c r="R6" t="n">
-        <v>1.872</v>
+        <v>1258.496</v>
       </c>
       <c r="S6" t="n">
-        <v>223.056</v>
+        <v>229.376</v>
       </c>
       <c r="T6" t="n">
-        <v>1275</v>
+        <v>1.4976</v>
       </c>
       <c r="U6" t="n">
-        <v>6834077.596661252</v>
+        <v>230.8736</v>
+      </c>
+      <c r="V6" t="n">
+        <v>1425</v>
+      </c>
+      <c r="W6" t="n">
+        <v>7018234.275311392</v>
       </c>
     </row>
     <row r="7">
@@ -902,34 +942,40 @@
         <v>6</v>
       </c>
       <c r="L7" t="n">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="M7" t="n">
+        <v>11</v>
+      </c>
+      <c r="N7" t="n">
+        <v>28</v>
+      </c>
+      <c r="O7" t="n">
         <v>4</v>
       </c>
-      <c r="N7" t="n">
-        <v>30</v>
-      </c>
-      <c r="O7" t="n">
+      <c r="P7" t="n">
+        <v>24</v>
+      </c>
+      <c r="Q7" t="n">
         <v>1</v>
       </c>
-      <c r="P7" t="n">
-        <v>1267.968</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>221.184</v>
-      </c>
       <c r="R7" t="n">
-        <v>1.872</v>
+        <v>1258.496</v>
       </c>
       <c r="S7" t="n">
-        <v>223.056</v>
+        <v>229.376</v>
       </c>
       <c r="T7" t="n">
-        <v>1275</v>
+        <v>1.4976</v>
       </c>
       <c r="U7" t="n">
-        <v>6675077.596661254</v>
+        <v>230.8736</v>
+      </c>
+      <c r="V7" t="n">
+        <v>1425</v>
+      </c>
+      <c r="W7" t="n">
+        <v>6859234.275311393</v>
       </c>
     </row>
     <row r="8">
@@ -969,34 +1015,40 @@
         <v>6</v>
       </c>
       <c r="L8" t="n">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="M8" t="n">
+        <v>11</v>
+      </c>
+      <c r="N8" t="n">
+        <v>28</v>
+      </c>
+      <c r="O8" t="n">
         <v>5</v>
       </c>
-      <c r="N8" t="n">
+      <c r="P8" t="n">
         <v>14</v>
       </c>
-      <c r="O8" t="n">
-        <v>1</v>
-      </c>
-      <c r="P8" t="n">
-        <v>1398.464</v>
-      </c>
       <c r="Q8" t="n">
-        <v>276.48</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>0.8735999999999999</v>
+        <v>1335.04</v>
       </c>
       <c r="S8" t="n">
-        <v>277.3536</v>
+        <v>286.72</v>
       </c>
       <c r="T8" t="n">
-        <v>1550</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>7898646.925555612</v>
+        <v>286.72</v>
+      </c>
+      <c r="V8" t="n">
+        <v>1625</v>
+      </c>
+      <c r="W8" t="n">
+        <v>8101665.728652061</v>
       </c>
     </row>
     <row r="9">
@@ -1036,33 +1088,39 @@
         <v>6</v>
       </c>
       <c r="L9" t="n">
+        <v>15</v>
+      </c>
+      <c r="M9" t="n">
+        <v>11</v>
+      </c>
+      <c r="N9" t="n">
         <v>27</v>
       </c>
-      <c r="M9" t="n">
+      <c r="O9" t="n">
         <v>5</v>
       </c>
-      <c r="N9" t="n">
-        <v>17</v>
-      </c>
-      <c r="O9" t="n">
+      <c r="P9" t="n">
+        <v>15</v>
+      </c>
+      <c r="Q9" t="n">
         <v>0</v>
       </c>
-      <c r="P9" t="n">
+      <c r="R9" t="n">
         <v>1287.36</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>276.48</v>
-      </c>
-      <c r="R9" t="n">
-        <v>0</v>
       </c>
       <c r="S9" t="n">
         <v>276.48</v>
       </c>
       <c r="T9" t="n">
-        <v>1575</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
+        <v>276.48</v>
+      </c>
+      <c r="V9" t="n">
+        <v>1550</v>
+      </c>
+      <c r="W9" t="n">
         <v>5924488.802757631</v>
       </c>
     </row>
@@ -1103,34 +1161,40 @@
         <v>6</v>
       </c>
       <c r="L10" t="n">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="M10" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="N10" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="O10" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="P10" t="n">
-        <v>1267.968</v>
+        <v>25</v>
       </c>
       <c r="Q10" t="n">
-        <v>221.184</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1.872</v>
+        <v>1335.04</v>
       </c>
       <c r="S10" t="n">
-        <v>223.056</v>
+        <v>286.72</v>
       </c>
       <c r="T10" t="n">
-        <v>1275</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>6790999.196661252</v>
+        <v>286.72</v>
+      </c>
+      <c r="V10" t="n">
+        <v>1375</v>
+      </c>
+      <c r="W10" t="n">
+        <v>7607744.206532921</v>
       </c>
     </row>
     <row r="11">
@@ -1170,33 +1234,39 @@
         <v>6</v>
       </c>
       <c r="L11" t="n">
+        <v>15</v>
+      </c>
+      <c r="M11" t="n">
+        <v>11</v>
+      </c>
+      <c r="N11" t="n">
         <v>28</v>
       </c>
-      <c r="M11" t="n">
+      <c r="O11" t="n">
         <v>5</v>
       </c>
-      <c r="N11" t="n">
-        <v>14</v>
-      </c>
-      <c r="O11" t="n">
+      <c r="P11" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q11" t="n">
         <v>0</v>
       </c>
-      <c r="P11" t="n">
+      <c r="R11" t="n">
         <v>1335.04</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>286.72</v>
-      </c>
-      <c r="R11" t="n">
-        <v>0</v>
       </c>
       <c r="S11" t="n">
         <v>286.72</v>
       </c>
       <c r="T11" t="n">
+        <v>0</v>
+      </c>
+      <c r="U11" t="n">
+        <v>286.72</v>
+      </c>
+      <c r="V11" t="n">
         <v>1550</v>
       </c>
-      <c r="U11" t="n">
+      <c r="W11" t="n">
         <v>7607744.206532921</v>
       </c>
     </row>
@@ -1237,33 +1307,39 @@
         <v>2</v>
       </c>
       <c r="L12" t="n">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="M12" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="N12" t="n">
         <v>26</v>
       </c>
       <c r="O12" t="n">
+        <v>4</v>
+      </c>
+      <c r="P12" t="n">
+        <v>26</v>
+      </c>
+      <c r="Q12" t="n">
         <v>2</v>
       </c>
-      <c r="P12" t="n">
+      <c r="R12" t="n">
         <v>1404.416</v>
       </c>
-      <c r="Q12" t="n">
+      <c r="S12" t="n">
         <v>212.992</v>
       </c>
-      <c r="R12" t="n">
+      <c r="T12" t="n">
         <v>3.2448</v>
       </c>
-      <c r="S12" t="n">
+      <c r="U12" t="n">
         <v>216.2368</v>
       </c>
-      <c r="T12" t="n">
+      <c r="V12" t="n">
         <v>1025</v>
       </c>
-      <c r="U12" t="n">
+      <c r="W12" t="n">
         <v>2601760.656935178</v>
       </c>
     </row>
@@ -1304,34 +1380,332 @@
         <v>10</v>
       </c>
       <c r="L13" t="n">
+        <v>15</v>
+      </c>
+      <c r="M13" t="n">
+        <v>11</v>
+      </c>
+      <c r="N13" t="n">
         <v>28</v>
       </c>
-      <c r="M13" t="n">
+      <c r="O13" t="n">
         <v>3</v>
       </c>
-      <c r="N13" t="n">
+      <c r="P13" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R13" t="n">
+        <v>801.024</v>
+      </c>
+      <c r="S13" t="n">
+        <v>172.032</v>
+      </c>
+      <c r="T13" t="n">
+        <v>0</v>
+      </c>
+      <c r="U13" t="n">
+        <v>172.032</v>
+      </c>
+      <c r="V13" t="n">
+        <v>1950</v>
+      </c>
+      <c r="W13" t="n">
+        <v>7798359.24584867</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Nm_b min</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>5.78</v>
+      </c>
+      <c r="D14" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="E14" t="n">
+        <v>10</v>
+      </c>
+      <c r="F14" t="n">
+        <v>53</v>
+      </c>
+      <c r="G14" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="H14" t="n">
+        <v>67.84</v>
+      </c>
+      <c r="I14" t="n">
+        <v>9.75</v>
+      </c>
+      <c r="J14" t="n">
+        <v>51.675</v>
+      </c>
+      <c r="K14" t="n">
+        <v>6</v>
+      </c>
+      <c r="L14" t="n">
+        <v>8</v>
+      </c>
+      <c r="M14" t="n">
+        <v>11</v>
+      </c>
+      <c r="N14" t="n">
+        <v>28</v>
+      </c>
+      <c r="O14" t="n">
+        <v>4</v>
+      </c>
+      <c r="P14" t="n">
+        <v>24</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>1</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1258.496</v>
+      </c>
+      <c r="S14" t="n">
+        <v>229.376</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1.4976</v>
+      </c>
+      <c r="U14" t="n">
+        <v>230.8736</v>
+      </c>
+      <c r="V14" t="n">
+        <v>1425</v>
+      </c>
+      <c r="W14" t="n">
+        <v>6965234.275311393</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Nm_b min</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>5.78</v>
+      </c>
+      <c r="D15" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="E15" t="n">
+        <v>10</v>
+      </c>
+      <c r="F15" t="n">
+        <v>53</v>
+      </c>
+      <c r="G15" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="H15" t="n">
+        <v>67.84</v>
+      </c>
+      <c r="I15" t="n">
+        <v>9.75</v>
+      </c>
+      <c r="J15" t="n">
+        <v>51.675</v>
+      </c>
+      <c r="K15" t="n">
+        <v>6</v>
+      </c>
+      <c r="L15" t="n">
+        <v>22</v>
+      </c>
+      <c r="M15" t="n">
+        <v>11</v>
+      </c>
+      <c r="N15" t="n">
+        <v>28</v>
+      </c>
+      <c r="O15" t="n">
+        <v>4</v>
+      </c>
+      <c r="P15" t="n">
+        <v>24</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>1</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1258.496</v>
+      </c>
+      <c r="S15" t="n">
+        <v>229.376</v>
+      </c>
+      <c r="T15" t="n">
+        <v>1.4976</v>
+      </c>
+      <c r="U15" t="n">
+        <v>230.8736</v>
+      </c>
+      <c r="V15" t="n">
+        <v>1425</v>
+      </c>
+      <c r="W15" t="n">
+        <v>6965234.275311393</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="n">
         <v>14</v>
       </c>
-      <c r="O13" t="n">
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Nm_uc min</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>5.78</v>
+      </c>
+      <c r="D16" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="E16" t="n">
+        <v>10</v>
+      </c>
+      <c r="F16" t="n">
+        <v>53</v>
+      </c>
+      <c r="G16" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="H16" t="n">
+        <v>67.84</v>
+      </c>
+      <c r="I16" t="n">
+        <v>9.75</v>
+      </c>
+      <c r="J16" t="n">
+        <v>51.675</v>
+      </c>
+      <c r="K16" t="n">
+        <v>6</v>
+      </c>
+      <c r="L16" t="n">
+        <v>15</v>
+      </c>
+      <c r="M16" t="n">
+        <v>6</v>
+      </c>
+      <c r="N16" t="n">
+        <v>28</v>
+      </c>
+      <c r="O16" t="n">
+        <v>4</v>
+      </c>
+      <c r="P16" t="n">
+        <v>24</v>
+      </c>
+      <c r="Q16" t="n">
         <v>1</v>
       </c>
-      <c r="P13" t="n">
-        <v>912.128</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>172.032</v>
-      </c>
-      <c r="R13" t="n">
-        <v>0.8735999999999999</v>
-      </c>
-      <c r="S13" t="n">
-        <v>172.9056</v>
-      </c>
-      <c r="T13" t="n">
-        <v>1950</v>
-      </c>
-      <c r="U13" t="n">
-        <v>7786784.045848669</v>
+      <c r="R16" t="n">
+        <v>1258.496</v>
+      </c>
+      <c r="S16" t="n">
+        <v>229.376</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1.4976</v>
+      </c>
+      <c r="U16" t="n">
+        <v>230.8736</v>
+      </c>
+      <c r="V16" t="n">
+        <v>1425</v>
+      </c>
+      <c r="W16" t="n">
+        <v>6965234.275311393</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Nm_uc min</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>5.78</v>
+      </c>
+      <c r="D17" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="E17" t="n">
+        <v>10</v>
+      </c>
+      <c r="F17" t="n">
+        <v>53</v>
+      </c>
+      <c r="G17" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="H17" t="n">
+        <v>67.84</v>
+      </c>
+      <c r="I17" t="n">
+        <v>9.75</v>
+      </c>
+      <c r="J17" t="n">
+        <v>51.675</v>
+      </c>
+      <c r="K17" t="n">
+        <v>6</v>
+      </c>
+      <c r="L17" t="n">
+        <v>15</v>
+      </c>
+      <c r="M17" t="n">
+        <v>18</v>
+      </c>
+      <c r="N17" t="n">
+        <v>28</v>
+      </c>
+      <c r="O17" t="n">
+        <v>4</v>
+      </c>
+      <c r="P17" t="n">
+        <v>24</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>1</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1258.496</v>
+      </c>
+      <c r="S17" t="n">
+        <v>229.376</v>
+      </c>
+      <c r="T17" t="n">
+        <v>1.4976</v>
+      </c>
+      <c r="U17" t="n">
+        <v>230.8736</v>
+      </c>
+      <c r="V17" t="n">
+        <v>1425</v>
+      </c>
+      <c r="W17" t="n">
+        <v>6965234.275311393</v>
       </c>
     </row>
   </sheetData>

--- a/Figuras/UMAX_18-10-24/UMAX_18-10-24_sensibilidade.xlsx
+++ b/Figuras/UMAX_18-10-24/UMAX_18-10-24_sensibilidade.xlsx
@@ -425,1287 +425,1309 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W17"/>
+  <dimension ref="A1:V18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Parametro variado</t>
+        </is>
+      </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Parametro variado</t>
+          <t>Preco Diesel [R$]</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Preco Diesel [R$]</t>
+          <t>Cotacao Dolar</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Cotacao Dolar</t>
+          <t>Preco Razao Elepot [USD]</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Preco Razao Elepot [USD]</t>
+          <t>Preco R.E. Cor. Dolar [R$]</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Preco R.E. Cor. Dolar [R$]</t>
+          <t>Preco Bat [USD]</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Preco Bat [USD]</t>
+          <t>Preco Bat Cor. Dolar [R$]</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>Preco Bat Cor. Dolar [R$]</t>
+          <t>Preco UC [USD]</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>Preco UC [USD]</t>
+          <t>Preco UC Cor. Dolar [R$]</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>Preco UC Cor. Dolar [R$]</t>
+          <t>C-rate</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>C-rate</t>
+          <t>Nm_b min</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>Nm_b min</t>
+          <t>Nm_uc min</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>Nm_uc min</t>
+          <t>Nm,b</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>Nm,b</t>
+          <t>Np,b</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>Np,b</t>
+          <t>Nm,uc</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>Nm,uc</t>
+          <t>Np,uc</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>Np,uc</t>
+          <t>Volume Total [L]</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>Volume Total [L]</t>
+          <t>Energia Total Bat. [kWh]</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>Energia Total Bat. [kWh]</t>
+          <t>Energia Total UC. [kWh]</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>Energia Total UC. [kWh]</t>
+          <t>Energia Total [kWh]</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>Energia Total [kWh]</t>
+          <t>Pth [kW]</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>Pth [kW]</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>VPL [R$]</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Preco Diesel</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>3.69</v>
+      </c>
+      <c r="C2" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="D2" t="n">
+        <v>10</v>
+      </c>
+      <c r="E2" t="n">
+        <v>53</v>
+      </c>
+      <c r="F2" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="G2" t="n">
+        <v>67.84</v>
+      </c>
+      <c r="H2" t="n">
+        <v>9.75</v>
+      </c>
+      <c r="I2" t="n">
+        <v>51.675</v>
+      </c>
+      <c r="J2" t="n">
+        <v>6</v>
+      </c>
+      <c r="K2" t="n">
+        <v>15</v>
+      </c>
+      <c r="L2" t="n">
+        <v>11</v>
+      </c>
+      <c r="M2" t="n">
+        <v>28</v>
+      </c>
+      <c r="N2" t="n">
+        <v>5</v>
+      </c>
+      <c r="O2" t="n">
+        <v>12</v>
+      </c>
+      <c r="P2" t="n">
         <v>0</v>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Preco Diesel</t>
-        </is>
-      </c>
-      <c r="C2" t="n">
-        <v>3.69</v>
-      </c>
-      <c r="D2" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="E2" t="n">
-        <v>10</v>
-      </c>
-      <c r="F2" t="n">
-        <v>53</v>
-      </c>
-      <c r="G2" t="n">
-        <v>12.8</v>
-      </c>
-      <c r="H2" t="n">
-        <v>67.84</v>
-      </c>
-      <c r="I2" t="n">
-        <v>9.75</v>
-      </c>
-      <c r="J2" t="n">
-        <v>51.675</v>
-      </c>
-      <c r="K2" t="n">
-        <v>6</v>
-      </c>
-      <c r="L2" t="n">
-        <v>15</v>
-      </c>
-      <c r="M2" t="n">
-        <v>11</v>
-      </c>
-      <c r="N2" t="n">
-        <v>28</v>
-      </c>
-      <c r="O2" t="n">
-        <v>5</v>
-      </c>
-      <c r="P2" t="n">
-        <v>12</v>
-      </c>
       <c r="Q2" t="n">
+        <v>1335.04</v>
+      </c>
+      <c r="R2" t="n">
+        <v>286.72</v>
+      </c>
+      <c r="S2" t="n">
         <v>0</v>
       </c>
-      <c r="R2" t="n">
-        <v>1335.04</v>
-      </c>
-      <c r="S2" t="n">
+      <c r="T2" t="n">
         <v>286.72</v>
       </c>
-      <c r="T2" t="n">
-        <v>0</v>
-      </c>
       <c r="U2" t="n">
-        <v>286.72</v>
+        <v>1150</v>
       </c>
       <c r="V2" t="n">
-        <v>1150</v>
-      </c>
-      <c r="W2" t="n">
         <v>4461322.518970323</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Preco Diesel</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>7.46</v>
+      </c>
+      <c r="C3" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="D3" t="n">
+        <v>10</v>
+      </c>
+      <c r="E3" t="n">
+        <v>53</v>
+      </c>
+      <c r="F3" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="G3" t="n">
+        <v>67.84</v>
+      </c>
+      <c r="H3" t="n">
+        <v>9.75</v>
+      </c>
+      <c r="I3" t="n">
+        <v>51.675</v>
+      </c>
+      <c r="J3" t="n">
+        <v>6</v>
+      </c>
+      <c r="K3" t="n">
+        <v>15</v>
+      </c>
+      <c r="L3" t="n">
+        <v>11</v>
+      </c>
+      <c r="M3" t="n">
+        <v>27</v>
+      </c>
+      <c r="N3" t="n">
+        <v>5</v>
+      </c>
+      <c r="O3" t="n">
+        <v>13</v>
+      </c>
+      <c r="P3" t="n">
         <v>1</v>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Preco Diesel</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
-        <v>7.46</v>
-      </c>
-      <c r="D3" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="E3" t="n">
-        <v>10</v>
-      </c>
-      <c r="F3" t="n">
-        <v>53</v>
-      </c>
-      <c r="G3" t="n">
-        <v>12.8</v>
-      </c>
-      <c r="H3" t="n">
-        <v>67.84</v>
-      </c>
-      <c r="I3" t="n">
-        <v>9.75</v>
-      </c>
-      <c r="J3" t="n">
-        <v>51.675</v>
-      </c>
-      <c r="K3" t="n">
-        <v>6</v>
-      </c>
-      <c r="L3" t="n">
-        <v>15</v>
-      </c>
-      <c r="M3" t="n">
-        <v>11</v>
-      </c>
-      <c r="N3" t="n">
-        <v>27</v>
-      </c>
-      <c r="O3" t="n">
-        <v>5</v>
-      </c>
-      <c r="P3" t="n">
-        <v>13</v>
-      </c>
       <c r="Q3" t="n">
-        <v>1</v>
+        <v>1390.528</v>
       </c>
       <c r="R3" t="n">
-        <v>1390.528</v>
+        <v>276.48</v>
       </c>
       <c r="S3" t="n">
-        <v>276.48</v>
+        <v>0.8111999999999999</v>
       </c>
       <c r="T3" t="n">
-        <v>0.8111999999999999</v>
+        <v>277.2912</v>
       </c>
       <c r="U3" t="n">
-        <v>277.2912</v>
+        <v>1400</v>
       </c>
       <c r="V3" t="n">
-        <v>1400</v>
-      </c>
-      <c r="W3" t="n">
         <v>9466060.856189825</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="B4" t="inlineStr">
+      <c r="A4" t="inlineStr">
         <is>
           <t>Cotacao Dolar</t>
         </is>
       </c>
+      <c r="B4" t="n">
+        <v>5.78</v>
+      </c>
       <c r="C4" t="n">
-        <v>5.78</v>
+        <v>4.58</v>
       </c>
       <c r="D4" t="n">
-        <v>4.58</v>
+        <v>10</v>
       </c>
       <c r="E4" t="n">
-        <v>10</v>
+        <v>45.8</v>
       </c>
       <c r="F4" t="n">
-        <v>45.8</v>
+        <v>12.8</v>
       </c>
       <c r="G4" t="n">
-        <v>12.8</v>
+        <v>58.624</v>
       </c>
       <c r="H4" t="n">
-        <v>58.624</v>
+        <v>9.75</v>
       </c>
       <c r="I4" t="n">
-        <v>9.75</v>
+        <v>44.655</v>
       </c>
       <c r="J4" t="n">
-        <v>44.655</v>
+        <v>6</v>
       </c>
       <c r="K4" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="L4" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="M4" t="n">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="N4" t="n">
-        <v>28</v>
+        <v>4</v>
       </c>
       <c r="O4" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="P4" t="n">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="Q4" t="n">
-        <v>1</v>
+        <v>1234.688</v>
       </c>
       <c r="R4" t="n">
-        <v>1234.688</v>
+        <v>229.376</v>
       </c>
       <c r="S4" t="n">
-        <v>229.376</v>
+        <v>1.3104</v>
       </c>
       <c r="T4" t="n">
-        <v>1.3104</v>
+        <v>230.6864</v>
       </c>
       <c r="U4" t="n">
-        <v>230.6864</v>
+        <v>1375</v>
       </c>
       <c r="V4" t="n">
-        <v>1375</v>
-      </c>
-      <c r="W4" t="n">
         <v>7143157.39965963</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="B5" t="inlineStr">
+      <c r="A5" t="inlineStr">
         <is>
           <t>Cotacao Dolar</t>
         </is>
       </c>
+      <c r="B5" t="n">
+        <v>5.78</v>
+      </c>
       <c r="C5" t="n">
-        <v>5.78</v>
+        <v>6.31</v>
       </c>
       <c r="D5" t="n">
-        <v>6.31</v>
+        <v>10</v>
       </c>
       <c r="E5" t="n">
-        <v>10</v>
+        <v>63.09999999999999</v>
       </c>
       <c r="F5" t="n">
-        <v>63.09999999999999</v>
+        <v>12.8</v>
       </c>
       <c r="G5" t="n">
-        <v>12.8</v>
+        <v>80.768</v>
       </c>
       <c r="H5" t="n">
-        <v>80.768</v>
+        <v>9.75</v>
       </c>
       <c r="I5" t="n">
-        <v>9.75</v>
+        <v>61.52249999999999</v>
       </c>
       <c r="J5" t="n">
-        <v>61.52249999999999</v>
+        <v>6</v>
       </c>
       <c r="K5" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="L5" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="M5" t="n">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="N5" t="n">
-        <v>28</v>
+        <v>5</v>
       </c>
       <c r="O5" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="P5" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
+        <v>1335.04</v>
+      </c>
+      <c r="R5" t="n">
+        <v>286.72</v>
+      </c>
+      <c r="S5" t="n">
         <v>0</v>
       </c>
-      <c r="R5" t="n">
-        <v>1335.04</v>
-      </c>
-      <c r="S5" t="n">
+      <c r="T5" t="n">
         <v>286.72</v>
       </c>
-      <c r="T5" t="n">
-        <v>0</v>
-      </c>
       <c r="U5" t="n">
-        <v>286.72</v>
+        <v>1225</v>
       </c>
       <c r="V5" t="n">
-        <v>1225</v>
-      </c>
-      <c r="W5" t="n">
         <v>7399294.871687513</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Preco Razao Elepot</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>5.78</v>
+      </c>
+      <c r="C6" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="D6" t="n">
+        <v>5</v>
+      </c>
+      <c r="E6" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="F6" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="G6" t="n">
+        <v>67.84</v>
+      </c>
+      <c r="H6" t="n">
+        <v>9.75</v>
+      </c>
+      <c r="I6" t="n">
+        <v>51.675</v>
+      </c>
+      <c r="J6" t="n">
+        <v>6</v>
+      </c>
+      <c r="K6" t="n">
+        <v>15</v>
+      </c>
+      <c r="L6" t="n">
+        <v>11</v>
+      </c>
+      <c r="M6" t="n">
+        <v>28</v>
+      </c>
+      <c r="N6" t="n">
         <v>4</v>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Preco Razao Elepot</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>5.78</v>
-      </c>
-      <c r="D6" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="E6" t="n">
-        <v>5</v>
-      </c>
-      <c r="F6" t="n">
-        <v>26.5</v>
-      </c>
-      <c r="G6" t="n">
-        <v>12.8</v>
-      </c>
-      <c r="H6" t="n">
-        <v>67.84</v>
-      </c>
-      <c r="I6" t="n">
-        <v>9.75</v>
-      </c>
-      <c r="J6" t="n">
-        <v>51.675</v>
-      </c>
-      <c r="K6" t="n">
-        <v>6</v>
-      </c>
-      <c r="L6" t="n">
-        <v>15</v>
-      </c>
-      <c r="M6" t="n">
-        <v>11</v>
-      </c>
-      <c r="N6" t="n">
-        <v>28</v>
-      </c>
       <c r="O6" t="n">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="P6" t="n">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="Q6" t="n">
-        <v>1</v>
+        <v>1258.496</v>
       </c>
       <c r="R6" t="n">
-        <v>1258.496</v>
+        <v>229.376</v>
       </c>
       <c r="S6" t="n">
-        <v>229.376</v>
+        <v>1.4976</v>
       </c>
       <c r="T6" t="n">
-        <v>1.4976</v>
+        <v>230.8736</v>
       </c>
       <c r="U6" t="n">
-        <v>230.8736</v>
+        <v>1425</v>
       </c>
       <c r="V6" t="n">
-        <v>1425</v>
-      </c>
-      <c r="W6" t="n">
         <v>7018234.275311392</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
-        <v>5</v>
-      </c>
-      <c r="B7" t="inlineStr">
+      <c r="A7" t="inlineStr">
         <is>
           <t>Preco Razao Elepot</t>
         </is>
       </c>
+      <c r="B7" t="n">
+        <v>5.78</v>
+      </c>
       <c r="C7" t="n">
-        <v>5.78</v>
+        <v>5.3</v>
       </c>
       <c r="D7" t="n">
-        <v>5.3</v>
+        <v>20</v>
       </c>
       <c r="E7" t="n">
-        <v>20</v>
+        <v>106</v>
       </c>
       <c r="F7" t="n">
-        <v>106</v>
+        <v>12.8</v>
       </c>
       <c r="G7" t="n">
-        <v>12.8</v>
+        <v>67.84</v>
       </c>
       <c r="H7" t="n">
-        <v>67.84</v>
+        <v>9.75</v>
       </c>
       <c r="I7" t="n">
-        <v>9.75</v>
+        <v>51.675</v>
       </c>
       <c r="J7" t="n">
-        <v>51.675</v>
+        <v>6</v>
       </c>
       <c r="K7" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="L7" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="M7" t="n">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="N7" t="n">
-        <v>28</v>
+        <v>4</v>
       </c>
       <c r="O7" t="n">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="P7" t="n">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="Q7" t="n">
-        <v>1</v>
+        <v>1258.496</v>
       </c>
       <c r="R7" t="n">
-        <v>1258.496</v>
+        <v>229.376</v>
       </c>
       <c r="S7" t="n">
-        <v>229.376</v>
+        <v>1.4976</v>
       </c>
       <c r="T7" t="n">
-        <v>1.4976</v>
+        <v>230.8736</v>
       </c>
       <c r="U7" t="n">
-        <v>230.8736</v>
+        <v>1425</v>
       </c>
       <c r="V7" t="n">
-        <v>1425</v>
-      </c>
-      <c r="W7" t="n">
         <v>6859234.275311393</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Preco Bat</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>5.78</v>
+      </c>
+      <c r="C8" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="D8" t="n">
+        <v>10</v>
+      </c>
+      <c r="E8" t="n">
+        <v>53</v>
+      </c>
+      <c r="F8" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="G8" t="n">
+        <v>33.92</v>
+      </c>
+      <c r="H8" t="n">
+        <v>9.75</v>
+      </c>
+      <c r="I8" t="n">
+        <v>51.675</v>
+      </c>
+      <c r="J8" t="n">
         <v>6</v>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Preco Bat</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>5.78</v>
-      </c>
-      <c r="D8" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="E8" t="n">
-        <v>10</v>
-      </c>
-      <c r="F8" t="n">
-        <v>53</v>
-      </c>
-      <c r="G8" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="H8" t="n">
-        <v>33.92</v>
-      </c>
-      <c r="I8" t="n">
-        <v>9.75</v>
-      </c>
-      <c r="J8" t="n">
-        <v>51.675</v>
-      </c>
       <c r="K8" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="L8" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="M8" t="n">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="N8" t="n">
-        <v>28</v>
+        <v>5</v>
       </c>
       <c r="O8" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="P8" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
+        <v>1335.04</v>
+      </c>
+      <c r="R8" t="n">
+        <v>286.72</v>
+      </c>
+      <c r="S8" t="n">
         <v>0</v>
       </c>
-      <c r="R8" t="n">
-        <v>1335.04</v>
-      </c>
-      <c r="S8" t="n">
+      <c r="T8" t="n">
         <v>286.72</v>
       </c>
-      <c r="T8" t="n">
-        <v>0</v>
-      </c>
       <c r="U8" t="n">
-        <v>286.72</v>
+        <v>1625</v>
       </c>
       <c r="V8" t="n">
-        <v>1625</v>
-      </c>
-      <c r="W8" t="n">
         <v>8101665.728652061</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
-        <v>7</v>
-      </c>
-      <c r="B9" t="inlineStr">
+      <c r="A9" t="inlineStr">
         <is>
           <t>Preco Bat</t>
         </is>
       </c>
+      <c r="B9" t="n">
+        <v>5.78</v>
+      </c>
       <c r="C9" t="n">
-        <v>5.78</v>
+        <v>5.3</v>
       </c>
       <c r="D9" t="n">
-        <v>5.3</v>
+        <v>10</v>
       </c>
       <c r="E9" t="n">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="F9" t="n">
-        <v>53</v>
+        <v>34.688</v>
       </c>
       <c r="G9" t="n">
-        <v>34.688</v>
+        <v>183.8464</v>
       </c>
       <c r="H9" t="n">
-        <v>183.8464</v>
+        <v>9.75</v>
       </c>
       <c r="I9" t="n">
-        <v>9.75</v>
+        <v>51.675</v>
       </c>
       <c r="J9" t="n">
-        <v>51.675</v>
+        <v>6</v>
       </c>
       <c r="K9" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="L9" t="n">
+        <v>11</v>
+      </c>
+      <c r="M9" t="n">
+        <v>27</v>
+      </c>
+      <c r="N9" t="n">
+        <v>5</v>
+      </c>
+      <c r="O9" t="n">
         <v>15</v>
       </c>
-      <c r="M9" t="n">
-        <v>11</v>
-      </c>
-      <c r="N9" t="n">
-        <v>27</v>
-      </c>
-      <c r="O9" t="n">
-        <v>5</v>
-      </c>
       <c r="P9" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
+        <v>1287.36</v>
+      </c>
+      <c r="R9" t="n">
+        <v>276.48</v>
+      </c>
+      <c r="S9" t="n">
         <v>0</v>
       </c>
-      <c r="R9" t="n">
-        <v>1287.36</v>
-      </c>
-      <c r="S9" t="n">
+      <c r="T9" t="n">
         <v>276.48</v>
       </c>
-      <c r="T9" t="n">
-        <v>0</v>
-      </c>
       <c r="U9" t="n">
-        <v>276.48</v>
+        <v>1550</v>
       </c>
       <c r="V9" t="n">
-        <v>1550</v>
-      </c>
-      <c r="W9" t="n">
         <v>5924488.802757631</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
-        <v>8</v>
-      </c>
-      <c r="B10" t="inlineStr">
+      <c r="A10" t="inlineStr">
         <is>
           <t>Preco UC</t>
         </is>
       </c>
+      <c r="B10" t="n">
+        <v>5.78</v>
+      </c>
       <c r="C10" t="n">
-        <v>5.78</v>
+        <v>5.3</v>
       </c>
       <c r="D10" t="n">
-        <v>5.3</v>
+        <v>10</v>
       </c>
       <c r="E10" t="n">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="F10" t="n">
-        <v>53</v>
+        <v>12.8</v>
       </c>
       <c r="G10" t="n">
-        <v>12.8</v>
+        <v>67.84</v>
       </c>
       <c r="H10" t="n">
-        <v>67.84</v>
+        <v>5.85</v>
       </c>
       <c r="I10" t="n">
-        <v>5.85</v>
+        <v>31.005</v>
       </c>
       <c r="J10" t="n">
-        <v>31.005</v>
+        <v>6</v>
       </c>
       <c r="K10" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="L10" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="M10" t="n">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="N10" t="n">
-        <v>28</v>
+        <v>5</v>
       </c>
       <c r="O10" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="P10" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
+        <v>1335.04</v>
+      </c>
+      <c r="R10" t="n">
+        <v>286.72</v>
+      </c>
+      <c r="S10" t="n">
         <v>0</v>
       </c>
-      <c r="R10" t="n">
-        <v>1335.04</v>
-      </c>
-      <c r="S10" t="n">
+      <c r="T10" t="n">
         <v>286.72</v>
       </c>
-      <c r="T10" t="n">
-        <v>0</v>
-      </c>
       <c r="U10" t="n">
-        <v>286.72</v>
+        <v>1375</v>
       </c>
       <c r="V10" t="n">
-        <v>1375</v>
-      </c>
-      <c r="W10" t="n">
         <v>7607744.206532921</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
-        <v>9</v>
-      </c>
-      <c r="B11" t="inlineStr">
+      <c r="A11" t="inlineStr">
         <is>
           <t>Preco UC</t>
         </is>
       </c>
+      <c r="B11" t="n">
+        <v>5.78</v>
+      </c>
       <c r="C11" t="n">
-        <v>5.78</v>
+        <v>5.3</v>
       </c>
       <c r="D11" t="n">
-        <v>5.3</v>
+        <v>10</v>
       </c>
       <c r="E11" t="n">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="F11" t="n">
-        <v>53</v>
+        <v>12.8</v>
       </c>
       <c r="G11" t="n">
-        <v>12.8</v>
+        <v>67.84</v>
       </c>
       <c r="H11" t="n">
-        <v>67.84</v>
+        <v>13.65</v>
       </c>
       <c r="I11" t="n">
-        <v>13.65</v>
+        <v>72.345</v>
       </c>
       <c r="J11" t="n">
-        <v>72.345</v>
+        <v>6</v>
       </c>
       <c r="K11" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="L11" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="M11" t="n">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="N11" t="n">
-        <v>28</v>
+        <v>5</v>
       </c>
       <c r="O11" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="P11" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
+        <v>1335.04</v>
+      </c>
+      <c r="R11" t="n">
+        <v>286.72</v>
+      </c>
+      <c r="S11" t="n">
         <v>0</v>
       </c>
-      <c r="R11" t="n">
-        <v>1335.04</v>
-      </c>
-      <c r="S11" t="n">
+      <c r="T11" t="n">
         <v>286.72</v>
       </c>
-      <c r="T11" t="n">
-        <v>0</v>
-      </c>
       <c r="U11" t="n">
-        <v>286.72</v>
+        <v>1550</v>
       </c>
       <c r="V11" t="n">
-        <v>1550</v>
-      </c>
-      <c r="W11" t="n">
         <v>7607744.206532921</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>C-rate</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>5.78</v>
+      </c>
+      <c r="C12" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="D12" t="n">
         <v>10</v>
       </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>C-rate</t>
-        </is>
-      </c>
-      <c r="C12" t="n">
-        <v>5.78</v>
-      </c>
-      <c r="D12" t="n">
-        <v>5.3</v>
-      </c>
       <c r="E12" t="n">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="F12" t="n">
-        <v>53</v>
+        <v>12.8</v>
       </c>
       <c r="G12" t="n">
-        <v>12.8</v>
+        <v>67.84</v>
       </c>
       <c r="H12" t="n">
-        <v>67.84</v>
+        <v>9.75</v>
       </c>
       <c r="I12" t="n">
-        <v>9.75</v>
+        <v>51.675</v>
       </c>
       <c r="J12" t="n">
-        <v>51.675</v>
+        <v>2</v>
       </c>
       <c r="K12" t="n">
+        <v>15</v>
+      </c>
+      <c r="L12" t="n">
+        <v>11</v>
+      </c>
+      <c r="M12" t="n">
+        <v>26</v>
+      </c>
+      <c r="N12" t="n">
+        <v>4</v>
+      </c>
+      <c r="O12" t="n">
+        <v>26</v>
+      </c>
+      <c r="P12" t="n">
         <v>2</v>
       </c>
-      <c r="L12" t="n">
-        <v>15</v>
-      </c>
-      <c r="M12" t="n">
-        <v>11</v>
-      </c>
-      <c r="N12" t="n">
-        <v>26</v>
-      </c>
-      <c r="O12" t="n">
-        <v>4</v>
-      </c>
-      <c r="P12" t="n">
-        <v>26</v>
-      </c>
       <c r="Q12" t="n">
-        <v>2</v>
+        <v>1404.416</v>
       </c>
       <c r="R12" t="n">
-        <v>1404.416</v>
+        <v>212.992</v>
       </c>
       <c r="S12" t="n">
-        <v>212.992</v>
+        <v>3.2448</v>
       </c>
       <c r="T12" t="n">
-        <v>3.2448</v>
+        <v>216.2368</v>
       </c>
       <c r="U12" t="n">
-        <v>216.2368</v>
+        <v>1025</v>
       </c>
       <c r="V12" t="n">
-        <v>1025</v>
-      </c>
-      <c r="W12" t="n">
         <v>2601760.656935178</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>C-rate</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>5.78</v>
+      </c>
+      <c r="C13" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="D13" t="n">
+        <v>10</v>
+      </c>
+      <c r="E13" t="n">
+        <v>53</v>
+      </c>
+      <c r="F13" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="G13" t="n">
+        <v>67.84</v>
+      </c>
+      <c r="H13" t="n">
+        <v>9.75</v>
+      </c>
+      <c r="I13" t="n">
+        <v>51.675</v>
+      </c>
+      <c r="J13" t="n">
+        <v>10</v>
+      </c>
+      <c r="K13" t="n">
+        <v>15</v>
+      </c>
+      <c r="L13" t="n">
         <v>11</v>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>C-rate</t>
-        </is>
-      </c>
-      <c r="C13" t="n">
-        <v>5.78</v>
-      </c>
-      <c r="D13" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="E13" t="n">
-        <v>10</v>
-      </c>
-      <c r="F13" t="n">
-        <v>53</v>
-      </c>
-      <c r="G13" t="n">
-        <v>12.8</v>
-      </c>
-      <c r="H13" t="n">
-        <v>67.84</v>
-      </c>
-      <c r="I13" t="n">
-        <v>9.75</v>
-      </c>
-      <c r="J13" t="n">
-        <v>51.675</v>
-      </c>
-      <c r="K13" t="n">
-        <v>10</v>
-      </c>
-      <c r="L13" t="n">
-        <v>15</v>
-      </c>
       <c r="M13" t="n">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="N13" t="n">
-        <v>28</v>
+        <v>3</v>
       </c>
       <c r="O13" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="P13" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
+        <v>801.024</v>
+      </c>
+      <c r="R13" t="n">
+        <v>172.032</v>
+      </c>
+      <c r="S13" t="n">
         <v>0</v>
       </c>
-      <c r="R13" t="n">
-        <v>801.024</v>
-      </c>
-      <c r="S13" t="n">
+      <c r="T13" t="n">
         <v>172.032</v>
       </c>
-      <c r="T13" t="n">
-        <v>0</v>
-      </c>
       <c r="U13" t="n">
-        <v>172.032</v>
+        <v>1950</v>
       </c>
       <c r="V13" t="n">
-        <v>1950</v>
-      </c>
-      <c r="W13" t="n">
         <v>7798359.24584867</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
-        <v>12</v>
-      </c>
-      <c r="B14" t="inlineStr">
+      <c r="A14" t="inlineStr">
         <is>
           <t>Nm_b min</t>
         </is>
       </c>
+      <c r="B14" t="n">
+        <v>5.78</v>
+      </c>
       <c r="C14" t="n">
-        <v>5.78</v>
+        <v>5.3</v>
       </c>
       <c r="D14" t="n">
-        <v>5.3</v>
+        <v>10</v>
       </c>
       <c r="E14" t="n">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="F14" t="n">
-        <v>53</v>
+        <v>12.8</v>
       </c>
       <c r="G14" t="n">
-        <v>12.8</v>
+        <v>67.84</v>
       </c>
       <c r="H14" t="n">
-        <v>67.84</v>
+        <v>9.75</v>
       </c>
       <c r="I14" t="n">
-        <v>9.75</v>
+        <v>51.675</v>
       </c>
       <c r="J14" t="n">
-        <v>51.675</v>
+        <v>6</v>
       </c>
       <c r="K14" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="L14" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="M14" t="n">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="N14" t="n">
-        <v>28</v>
+        <v>4</v>
       </c>
       <c r="O14" t="n">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="P14" t="n">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="Q14" t="n">
-        <v>1</v>
+        <v>1258.496</v>
       </c>
       <c r="R14" t="n">
-        <v>1258.496</v>
+        <v>229.376</v>
       </c>
       <c r="S14" t="n">
-        <v>229.376</v>
+        <v>1.4976</v>
       </c>
       <c r="T14" t="n">
-        <v>1.4976</v>
+        <v>230.8736</v>
       </c>
       <c r="U14" t="n">
-        <v>230.8736</v>
+        <v>1425</v>
       </c>
       <c r="V14" t="n">
-        <v>1425</v>
-      </c>
-      <c r="W14" t="n">
         <v>6965234.275311393</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
-        <v>13</v>
-      </c>
-      <c r="B15" t="inlineStr">
+      <c r="A15" t="inlineStr">
         <is>
           <t>Nm_b min</t>
         </is>
       </c>
+      <c r="B15" t="n">
+        <v>5.78</v>
+      </c>
       <c r="C15" t="n">
-        <v>5.78</v>
+        <v>5.3</v>
       </c>
       <c r="D15" t="n">
-        <v>5.3</v>
+        <v>10</v>
       </c>
       <c r="E15" t="n">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="F15" t="n">
-        <v>53</v>
+        <v>12.8</v>
       </c>
       <c r="G15" t="n">
-        <v>12.8</v>
+        <v>67.84</v>
       </c>
       <c r="H15" t="n">
-        <v>67.84</v>
+        <v>9.75</v>
       </c>
       <c r="I15" t="n">
-        <v>9.75</v>
+        <v>51.675</v>
       </c>
       <c r="J15" t="n">
-        <v>51.675</v>
+        <v>6</v>
       </c>
       <c r="K15" t="n">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="L15" t="n">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="M15" t="n">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="N15" t="n">
-        <v>28</v>
+        <v>4</v>
       </c>
       <c r="O15" t="n">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="P15" t="n">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="Q15" t="n">
-        <v>1</v>
+        <v>1258.496</v>
       </c>
       <c r="R15" t="n">
-        <v>1258.496</v>
+        <v>229.376</v>
       </c>
       <c r="S15" t="n">
-        <v>229.376</v>
+        <v>1.4976</v>
       </c>
       <c r="T15" t="n">
-        <v>1.4976</v>
+        <v>230.8736</v>
       </c>
       <c r="U15" t="n">
-        <v>230.8736</v>
+        <v>1425</v>
       </c>
       <c r="V15" t="n">
-        <v>1425</v>
-      </c>
-      <c r="W15" t="n">
         <v>6965234.275311393</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
-        <v>14</v>
-      </c>
-      <c r="B16" t="inlineStr">
+      <c r="A16" t="inlineStr">
         <is>
           <t>Nm_uc min</t>
         </is>
       </c>
+      <c r="B16" t="n">
+        <v>5.78</v>
+      </c>
       <c r="C16" t="n">
-        <v>5.78</v>
+        <v>5.3</v>
       </c>
       <c r="D16" t="n">
-        <v>5.3</v>
+        <v>10</v>
       </c>
       <c r="E16" t="n">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="F16" t="n">
-        <v>53</v>
+        <v>12.8</v>
       </c>
       <c r="G16" t="n">
-        <v>12.8</v>
+        <v>67.84</v>
       </c>
       <c r="H16" t="n">
-        <v>67.84</v>
+        <v>9.75</v>
       </c>
       <c r="I16" t="n">
-        <v>9.75</v>
+        <v>51.675</v>
       </c>
       <c r="J16" t="n">
-        <v>51.675</v>
+        <v>6</v>
       </c>
       <c r="K16" t="n">
+        <v>15</v>
+      </c>
+      <c r="L16" t="n">
         <v>6</v>
       </c>
-      <c r="L16" t="n">
-        <v>15</v>
-      </c>
       <c r="M16" t="n">
-        <v>6</v>
+        <v>28</v>
       </c>
       <c r="N16" t="n">
-        <v>28</v>
+        <v>4</v>
       </c>
       <c r="O16" t="n">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="P16" t="n">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="Q16" t="n">
-        <v>1</v>
+        <v>1258.496</v>
       </c>
       <c r="R16" t="n">
-        <v>1258.496</v>
+        <v>229.376</v>
       </c>
       <c r="S16" t="n">
-        <v>229.376</v>
+        <v>1.4976</v>
       </c>
       <c r="T16" t="n">
-        <v>1.4976</v>
+        <v>230.8736</v>
       </c>
       <c r="U16" t="n">
-        <v>230.8736</v>
+        <v>1425</v>
       </c>
       <c r="V16" t="n">
-        <v>1425</v>
-      </c>
-      <c r="W16" t="n">
         <v>6965234.275311393</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Nm_uc min</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>5.78</v>
+      </c>
+      <c r="C17" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="D17" t="n">
+        <v>10</v>
+      </c>
+      <c r="E17" t="n">
+        <v>53</v>
+      </c>
+      <c r="F17" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="G17" t="n">
+        <v>67.84</v>
+      </c>
+      <c r="H17" t="n">
+        <v>9.75</v>
+      </c>
+      <c r="I17" t="n">
+        <v>51.675</v>
+      </c>
+      <c r="J17" t="n">
+        <v>6</v>
+      </c>
+      <c r="K17" t="n">
         <v>15</v>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Nm_uc min</t>
-        </is>
-      </c>
-      <c r="C17" t="n">
+      <c r="L17" t="n">
+        <v>18</v>
+      </c>
+      <c r="M17" t="n">
+        <v>28</v>
+      </c>
+      <c r="N17" t="n">
+        <v>4</v>
+      </c>
+      <c r="O17" t="n">
+        <v>24</v>
+      </c>
+      <c r="P17" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>1258.496</v>
+      </c>
+      <c r="R17" t="n">
+        <v>229.376</v>
+      </c>
+      <c r="S17" t="n">
+        <v>1.4976</v>
+      </c>
+      <c r="T17" t="n">
+        <v>230.8736</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1425</v>
+      </c>
+      <c r="V17" t="n">
+        <v>6965234.275311393</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Caso base</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
         <v>5.78</v>
       </c>
-      <c r="D17" t="n">
+      <c r="C18" t="n">
         <v>5.3</v>
       </c>
-      <c r="E17" t="n">
+      <c r="D18" t="n">
         <v>10</v>
       </c>
-      <c r="F17" t="n">
+      <c r="E18" t="n">
         <v>53</v>
       </c>
-      <c r="G17" t="n">
+      <c r="F18" t="n">
         <v>12.8</v>
       </c>
-      <c r="H17" t="n">
+      <c r="G18" t="n">
         <v>67.84</v>
       </c>
-      <c r="I17" t="n">
+      <c r="H18" t="n">
         <v>9.75</v>
       </c>
-      <c r="J17" t="n">
+      <c r="I18" t="n">
         <v>51.675</v>
       </c>
-      <c r="K17" t="n">
+      <c r="J18" t="n">
         <v>6</v>
       </c>
-      <c r="L17" t="n">
+      <c r="K18" t="n">
         <v>15</v>
       </c>
-      <c r="M17" t="n">
-        <v>18</v>
-      </c>
-      <c r="N17" t="n">
+      <c r="L18" t="n">
+        <v>11</v>
+      </c>
+      <c r="M18" t="n">
         <v>28</v>
       </c>
-      <c r="O17" t="n">
+      <c r="N18" t="n">
         <v>4</v>
       </c>
-      <c r="P17" t="n">
-        <v>24</v>
-      </c>
-      <c r="Q17" t="n">
+      <c r="O18" t="n">
+        <v>21</v>
+      </c>
+      <c r="P18" t="n">
         <v>1</v>
       </c>
-      <c r="R17" t="n">
-        <v>1258.496</v>
-      </c>
-      <c r="S17" t="n">
+      <c r="Q18" t="n">
+        <v>1234.688</v>
+      </c>
+      <c r="R18" t="n">
         <v>229.376</v>
       </c>
-      <c r="T17" t="n">
-        <v>1.4976</v>
-      </c>
-      <c r="U17" t="n">
-        <v>230.8736</v>
-      </c>
-      <c r="V17" t="n">
-        <v>1425</v>
-      </c>
-      <c r="W17" t="n">
-        <v>6965234.275311393</v>
+      <c r="S18" t="n">
+        <v>1.3104</v>
+      </c>
+      <c r="T18" t="n">
+        <v>230.6864</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1375</v>
+      </c>
+      <c r="V18" t="n">
+        <v>7006170.727263453</v>
       </c>
     </row>
   </sheetData>

--- a/Figuras/UMAX_18-10-24/UMAX_18-10-24_sensibilidade.xlsx
+++ b/Figuras/UMAX_18-10-24/UMAX_18-10-24_sensibilidade.xlsx
@@ -425,1308 +425,1359 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V18"/>
+  <dimension ref="A1:W18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Parametro variado</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Preco Diesel [R$]</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Cotacao Dolar</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Preco Razao Elepot [USD]</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Preco R.E. Cor. Dolar [R$]</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Preco Bat [USD]</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Preco Bat Cor. Dolar [R$]</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Preco UC [USD]</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Preco UC Cor. Dolar [R$]</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>C-rate</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Nm_b min</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Nm_uc min</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Nm,b</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Np,b</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Nm,uc</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>Np,uc</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>Volume Total [L]</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>Energia Total Bat. [kWh]</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>Energia Total UC. [kWh]</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>Energia Total [kWh]</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>Pth [kW]</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>VPL [R$]</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Preco Diesel</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>3.69</v>
+      <c r="A2" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Caso base</t>
+        </is>
       </c>
       <c r="C2" t="n">
+        <v>5.78</v>
+      </c>
+      <c r="D2" t="n">
         <v>5.3</v>
       </c>
-      <c r="D2" t="n">
+      <c r="E2" t="n">
         <v>10</v>
       </c>
-      <c r="E2" t="n">
+      <c r="F2" t="n">
         <v>53</v>
       </c>
-      <c r="F2" t="n">
+      <c r="G2" t="n">
         <v>12.8</v>
       </c>
-      <c r="G2" t="n">
+      <c r="H2" t="n">
         <v>67.84</v>
       </c>
-      <c r="H2" t="n">
+      <c r="I2" t="n">
         <v>9.75</v>
       </c>
-      <c r="I2" t="n">
+      <c r="J2" t="n">
         <v>51.675</v>
       </c>
-      <c r="J2" t="n">
+      <c r="K2" t="n">
         <v>6</v>
       </c>
-      <c r="K2" t="n">
+      <c r="L2" t="n">
         <v>15</v>
       </c>
-      <c r="L2" t="n">
+      <c r="M2" t="n">
         <v>11</v>
       </c>
-      <c r="M2" t="n">
+      <c r="N2" t="n">
         <v>28</v>
       </c>
-      <c r="N2" t="n">
-        <v>5</v>
-      </c>
       <c r="O2" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="Q2" t="n">
-        <v>1335.04</v>
+        <v>1</v>
       </c>
       <c r="R2" t="n">
-        <v>286.72</v>
+        <v>1234.688</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>229.376</v>
       </c>
       <c r="T2" t="n">
-        <v>286.72</v>
+        <v>1.3104</v>
       </c>
       <c r="U2" t="n">
-        <v>1150</v>
+        <v>230.6864</v>
       </c>
       <c r="V2" t="n">
-        <v>4461322.518970323</v>
+        <v>1375</v>
+      </c>
+      <c r="W2" t="n">
+        <v>7006170.727263453</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" t="inlineStr">
         <is>
           <t>Preco Diesel</t>
         </is>
       </c>
-      <c r="B3" t="n">
-        <v>7.46</v>
-      </c>
       <c r="C3" t="n">
+        <v>3.69</v>
+      </c>
+      <c r="D3" t="n">
         <v>5.3</v>
       </c>
-      <c r="D3" t="n">
+      <c r="E3" t="n">
         <v>10</v>
       </c>
-      <c r="E3" t="n">
+      <c r="F3" t="n">
         <v>53</v>
       </c>
-      <c r="F3" t="n">
+      <c r="G3" t="n">
         <v>12.8</v>
       </c>
-      <c r="G3" t="n">
+      <c r="H3" t="n">
         <v>67.84</v>
       </c>
-      <c r="H3" t="n">
+      <c r="I3" t="n">
         <v>9.75</v>
       </c>
-      <c r="I3" t="n">
+      <c r="J3" t="n">
         <v>51.675</v>
       </c>
-      <c r="J3" t="n">
+      <c r="K3" t="n">
         <v>6</v>
       </c>
-      <c r="K3" t="n">
+      <c r="L3" t="n">
         <v>15</v>
       </c>
-      <c r="L3" t="n">
+      <c r="M3" t="n">
         <v>11</v>
       </c>
-      <c r="M3" t="n">
-        <v>27</v>
-      </c>
       <c r="N3" t="n">
+        <v>28</v>
+      </c>
+      <c r="O3" t="n">
         <v>5</v>
       </c>
-      <c r="O3" t="n">
-        <v>13</v>
-      </c>
       <c r="P3" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="Q3" t="n">
-        <v>1390.528</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>276.48</v>
+        <v>1335.04</v>
       </c>
       <c r="S3" t="n">
-        <v>0.8111999999999999</v>
+        <v>286.72</v>
       </c>
       <c r="T3" t="n">
-        <v>277.2912</v>
+        <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>1400</v>
+        <v>286.72</v>
       </c>
       <c r="V3" t="n">
-        <v>9466060.856189825</v>
+        <v>1100</v>
+      </c>
+      <c r="W3" t="n">
+        <v>4461322.518970323</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Cotacao Dolar</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>5.78</v>
+      <c r="A4" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Preco Diesel</t>
+        </is>
       </c>
       <c r="C4" t="n">
-        <v>4.58</v>
+        <v>7.46</v>
       </c>
       <c r="D4" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="E4" t="n">
         <v>10</v>
       </c>
-      <c r="E4" t="n">
-        <v>45.8</v>
-      </c>
       <c r="F4" t="n">
+        <v>53</v>
+      </c>
+      <c r="G4" t="n">
         <v>12.8</v>
       </c>
-      <c r="G4" t="n">
-        <v>58.624</v>
-      </c>
       <c r="H4" t="n">
+        <v>67.84</v>
+      </c>
+      <c r="I4" t="n">
         <v>9.75</v>
       </c>
-      <c r="I4" t="n">
-        <v>44.655</v>
-      </c>
       <c r="J4" t="n">
+        <v>51.675</v>
+      </c>
+      <c r="K4" t="n">
         <v>6</v>
       </c>
-      <c r="K4" t="n">
+      <c r="L4" t="n">
         <v>15</v>
       </c>
-      <c r="L4" t="n">
+      <c r="M4" t="n">
         <v>11</v>
       </c>
-      <c r="M4" t="n">
+      <c r="N4" t="n">
         <v>28</v>
       </c>
-      <c r="N4" t="n">
-        <v>4</v>
-      </c>
       <c r="O4" t="n">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="P4" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="Q4" t="n">
-        <v>1234.688</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>229.376</v>
+        <v>1335.04</v>
       </c>
       <c r="S4" t="n">
-        <v>1.3104</v>
+        <v>286.72</v>
       </c>
       <c r="T4" t="n">
-        <v>230.6864</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>1375</v>
+        <v>286.72</v>
       </c>
       <c r="V4" t="n">
-        <v>7143157.39965963</v>
+        <v>1425</v>
+      </c>
+      <c r="W4" t="n">
+        <v>10136925.27596123</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="B5" t="inlineStr">
         <is>
           <t>Cotacao Dolar</t>
         </is>
       </c>
-      <c r="B5" t="n">
+      <c r="C5" t="n">
         <v>5.78</v>
       </c>
-      <c r="C5" t="n">
-        <v>6.31</v>
-      </c>
       <c r="D5" t="n">
+        <v>4.58</v>
+      </c>
+      <c r="E5" t="n">
         <v>10</v>
       </c>
-      <c r="E5" t="n">
-        <v>63.09999999999999</v>
-      </c>
       <c r="F5" t="n">
+        <v>45.8</v>
+      </c>
+      <c r="G5" t="n">
         <v>12.8</v>
       </c>
-      <c r="G5" t="n">
-        <v>80.768</v>
-      </c>
       <c r="H5" t="n">
+        <v>58.624</v>
+      </c>
+      <c r="I5" t="n">
         <v>9.75</v>
       </c>
-      <c r="I5" t="n">
-        <v>61.52249999999999</v>
-      </c>
       <c r="J5" t="n">
+        <v>44.655</v>
+      </c>
+      <c r="K5" t="n">
         <v>6</v>
       </c>
-      <c r="K5" t="n">
+      <c r="L5" t="n">
         <v>15</v>
       </c>
-      <c r="L5" t="n">
+      <c r="M5" t="n">
         <v>11</v>
       </c>
-      <c r="M5" t="n">
+      <c r="N5" t="n">
         <v>28</v>
       </c>
-      <c r="N5" t="n">
-        <v>5</v>
-      </c>
       <c r="O5" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="Q5" t="n">
-        <v>1335.04</v>
+        <v>1</v>
       </c>
       <c r="R5" t="n">
-        <v>286.72</v>
+        <v>1234.688</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>229.376</v>
       </c>
       <c r="T5" t="n">
-        <v>286.72</v>
+        <v>1.3104</v>
       </c>
       <c r="U5" t="n">
-        <v>1225</v>
+        <v>230.6864</v>
       </c>
       <c r="V5" t="n">
-        <v>7399294.871687513</v>
+        <v>1375</v>
+      </c>
+      <c r="W5" t="n">
+        <v>7143157.39965963</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Preco Razao Elepot</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
+      <c r="A6" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Cotacao Dolar</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
         <v>5.78</v>
       </c>
-      <c r="C6" t="n">
-        <v>5.3</v>
-      </c>
       <c r="D6" t="n">
+        <v>6.31</v>
+      </c>
+      <c r="E6" t="n">
+        <v>10</v>
+      </c>
+      <c r="F6" t="n">
+        <v>63.09999999999999</v>
+      </c>
+      <c r="G6" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="H6" t="n">
+        <v>80.768</v>
+      </c>
+      <c r="I6" t="n">
+        <v>9.75</v>
+      </c>
+      <c r="J6" t="n">
+        <v>61.52249999999999</v>
+      </c>
+      <c r="K6" t="n">
+        <v>6</v>
+      </c>
+      <c r="L6" t="n">
+        <v>15</v>
+      </c>
+      <c r="M6" t="n">
+        <v>11</v>
+      </c>
+      <c r="N6" t="n">
+        <v>28</v>
+      </c>
+      <c r="O6" t="n">
         <v>5</v>
       </c>
-      <c r="E6" t="n">
-        <v>26.5</v>
-      </c>
-      <c r="F6" t="n">
-        <v>12.8</v>
-      </c>
-      <c r="G6" t="n">
-        <v>67.84</v>
-      </c>
-      <c r="H6" t="n">
-        <v>9.75</v>
-      </c>
-      <c r="I6" t="n">
-        <v>51.675</v>
-      </c>
-      <c r="J6" t="n">
-        <v>6</v>
-      </c>
-      <c r="K6" t="n">
-        <v>15</v>
-      </c>
-      <c r="L6" t="n">
-        <v>11</v>
-      </c>
-      <c r="M6" t="n">
-        <v>28</v>
-      </c>
-      <c r="N6" t="n">
-        <v>4</v>
-      </c>
-      <c r="O6" t="n">
-        <v>24</v>
-      </c>
       <c r="P6" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="Q6" t="n">
-        <v>1258.496</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>229.376</v>
+        <v>1335.04</v>
       </c>
       <c r="S6" t="n">
-        <v>1.4976</v>
+        <v>286.72</v>
       </c>
       <c r="T6" t="n">
-        <v>230.8736</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>1425</v>
+        <v>286.72</v>
       </c>
       <c r="V6" t="n">
-        <v>7018234.275311392</v>
+        <v>1225</v>
+      </c>
+      <c r="W6" t="n">
+        <v>7399294.871687513</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="B7" t="inlineStr">
         <is>
           <t>Preco Razao Elepot</t>
         </is>
       </c>
-      <c r="B7" t="n">
+      <c r="C7" t="n">
         <v>5.78</v>
       </c>
-      <c r="C7" t="n">
+      <c r="D7" t="n">
         <v>5.3</v>
       </c>
-      <c r="D7" t="n">
-        <v>20</v>
-      </c>
       <c r="E7" t="n">
-        <v>106</v>
+        <v>5</v>
       </c>
       <c r="F7" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="G7" t="n">
         <v>12.8</v>
       </c>
-      <c r="G7" t="n">
+      <c r="H7" t="n">
         <v>67.84</v>
       </c>
-      <c r="H7" t="n">
+      <c r="I7" t="n">
         <v>9.75</v>
       </c>
-      <c r="I7" t="n">
+      <c r="J7" t="n">
         <v>51.675</v>
       </c>
-      <c r="J7" t="n">
+      <c r="K7" t="n">
         <v>6</v>
       </c>
-      <c r="K7" t="n">
+      <c r="L7" t="n">
         <v>15</v>
       </c>
-      <c r="L7" t="n">
+      <c r="M7" t="n">
         <v>11</v>
       </c>
-      <c r="M7" t="n">
+      <c r="N7" t="n">
         <v>28</v>
       </c>
-      <c r="N7" t="n">
+      <c r="O7" t="n">
         <v>4</v>
       </c>
-      <c r="O7" t="n">
-        <v>24</v>
-      </c>
       <c r="P7" t="n">
+        <v>21</v>
+      </c>
+      <c r="Q7" t="n">
         <v>1</v>
       </c>
-      <c r="Q7" t="n">
-        <v>1258.496</v>
-      </c>
       <c r="R7" t="n">
+        <v>1234.688</v>
+      </c>
+      <c r="S7" t="n">
         <v>229.376</v>
       </c>
-      <c r="S7" t="n">
-        <v>1.4976</v>
-      </c>
       <c r="T7" t="n">
-        <v>230.8736</v>
+        <v>1.3104</v>
       </c>
       <c r="U7" t="n">
-        <v>1425</v>
+        <v>230.6864</v>
       </c>
       <c r="V7" t="n">
-        <v>6859234.275311393</v>
+        <v>1375</v>
+      </c>
+      <c r="W7" t="n">
+        <v>7059170.727263453</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Preco Bat</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
+      <c r="A8" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Preco Razao Elepot</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
         <v>5.78</v>
       </c>
-      <c r="C8" t="n">
+      <c r="D8" t="n">
         <v>5.3</v>
       </c>
-      <c r="D8" t="n">
-        <v>10</v>
-      </c>
       <c r="E8" t="n">
-        <v>53</v>
+        <v>20</v>
       </c>
       <c r="F8" t="n">
-        <v>6.4</v>
+        <v>106</v>
       </c>
       <c r="G8" t="n">
-        <v>33.92</v>
+        <v>12.8</v>
       </c>
       <c r="H8" t="n">
+        <v>67.84</v>
+      </c>
+      <c r="I8" t="n">
         <v>9.75</v>
       </c>
-      <c r="I8" t="n">
+      <c r="J8" t="n">
         <v>51.675</v>
       </c>
-      <c r="J8" t="n">
+      <c r="K8" t="n">
         <v>6</v>
       </c>
-      <c r="K8" t="n">
+      <c r="L8" t="n">
         <v>15</v>
       </c>
-      <c r="L8" t="n">
+      <c r="M8" t="n">
         <v>11</v>
       </c>
-      <c r="M8" t="n">
+      <c r="N8" t="n">
         <v>28</v>
       </c>
-      <c r="N8" t="n">
-        <v>5</v>
-      </c>
       <c r="O8" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="Q8" t="n">
-        <v>1335.04</v>
+        <v>1</v>
       </c>
       <c r="R8" t="n">
-        <v>286.72</v>
+        <v>1234.688</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>229.376</v>
       </c>
       <c r="T8" t="n">
-        <v>286.72</v>
+        <v>1.3104</v>
       </c>
       <c r="U8" t="n">
-        <v>1625</v>
+        <v>230.6864</v>
       </c>
       <c r="V8" t="n">
-        <v>8101665.728652061</v>
+        <v>1375</v>
+      </c>
+      <c r="W8" t="n">
+        <v>6900170.727263452</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="A9" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="B9" t="inlineStr">
         <is>
           <t>Preco Bat</t>
         </is>
       </c>
-      <c r="B9" t="n">
+      <c r="C9" t="n">
         <v>5.78</v>
       </c>
-      <c r="C9" t="n">
+      <c r="D9" t="n">
         <v>5.3</v>
       </c>
-      <c r="D9" t="n">
+      <c r="E9" t="n">
         <v>10</v>
       </c>
-      <c r="E9" t="n">
+      <c r="F9" t="n">
         <v>53</v>
       </c>
-      <c r="F9" t="n">
-        <v>34.688</v>
-      </c>
       <c r="G9" t="n">
-        <v>183.8464</v>
+        <v>6.4</v>
       </c>
       <c r="H9" t="n">
+        <v>33.92</v>
+      </c>
+      <c r="I9" t="n">
         <v>9.75</v>
       </c>
-      <c r="I9" t="n">
+      <c r="J9" t="n">
         <v>51.675</v>
       </c>
-      <c r="J9" t="n">
+      <c r="K9" t="n">
         <v>6</v>
       </c>
-      <c r="K9" t="n">
+      <c r="L9" t="n">
         <v>15</v>
       </c>
-      <c r="L9" t="n">
+      <c r="M9" t="n">
         <v>11</v>
       </c>
-      <c r="M9" t="n">
-        <v>27</v>
-      </c>
       <c r="N9" t="n">
+        <v>28</v>
+      </c>
+      <c r="O9" t="n">
         <v>5</v>
       </c>
-      <c r="O9" t="n">
-        <v>15</v>
-      </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="Q9" t="n">
-        <v>1287.36</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>276.48</v>
+        <v>1335.04</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>286.72</v>
       </c>
       <c r="T9" t="n">
-        <v>276.48</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>1550</v>
+        <v>286.72</v>
       </c>
       <c r="V9" t="n">
-        <v>5924488.802757631</v>
+        <v>1625</v>
+      </c>
+      <c r="W9" t="n">
+        <v>8101665.728652061</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Preco UC</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
+      <c r="A10" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Preco Bat</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
         <v>5.78</v>
       </c>
-      <c r="C10" t="n">
+      <c r="D10" t="n">
         <v>5.3</v>
       </c>
-      <c r="D10" t="n">
+      <c r="E10" t="n">
         <v>10</v>
       </c>
-      <c r="E10" t="n">
+      <c r="F10" t="n">
         <v>53</v>
       </c>
-      <c r="F10" t="n">
-        <v>12.8</v>
-      </c>
       <c r="G10" t="n">
-        <v>67.84</v>
+        <v>34.688</v>
       </c>
       <c r="H10" t="n">
-        <v>5.85</v>
+        <v>183.8464</v>
       </c>
       <c r="I10" t="n">
-        <v>31.005</v>
+        <v>9.75</v>
       </c>
       <c r="J10" t="n">
+        <v>51.675</v>
+      </c>
+      <c r="K10" t="n">
         <v>6</v>
       </c>
-      <c r="K10" t="n">
+      <c r="L10" t="n">
         <v>15</v>
       </c>
-      <c r="L10" t="n">
+      <c r="M10" t="n">
         <v>11</v>
       </c>
-      <c r="M10" t="n">
-        <v>28</v>
-      </c>
       <c r="N10" t="n">
+        <v>27</v>
+      </c>
+      <c r="O10" t="n">
         <v>5</v>
       </c>
-      <c r="O10" t="n">
-        <v>25</v>
-      </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="Q10" t="n">
-        <v>1335.04</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>286.72</v>
+        <v>1287.36</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>276.48</v>
       </c>
       <c r="T10" t="n">
-        <v>286.72</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>1375</v>
+        <v>276.48</v>
       </c>
       <c r="V10" t="n">
-        <v>7607744.206532921</v>
+        <v>1675</v>
+      </c>
+      <c r="W10" t="n">
+        <v>5924488.802757631</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
+      <c r="A11" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="B11" t="inlineStr">
         <is>
           <t>Preco UC</t>
         </is>
       </c>
-      <c r="B11" t="n">
+      <c r="C11" t="n">
         <v>5.78</v>
       </c>
-      <c r="C11" t="n">
+      <c r="D11" t="n">
         <v>5.3</v>
       </c>
-      <c r="D11" t="n">
+      <c r="E11" t="n">
         <v>10</v>
       </c>
-      <c r="E11" t="n">
+      <c r="F11" t="n">
         <v>53</v>
       </c>
-      <c r="F11" t="n">
+      <c r="G11" t="n">
         <v>12.8</v>
       </c>
-      <c r="G11" t="n">
+      <c r="H11" t="n">
         <v>67.84</v>
       </c>
-      <c r="H11" t="n">
-        <v>13.65</v>
-      </c>
       <c r="I11" t="n">
-        <v>72.345</v>
+        <v>5.85</v>
       </c>
       <c r="J11" t="n">
+        <v>31.005</v>
+      </c>
+      <c r="K11" t="n">
         <v>6</v>
       </c>
-      <c r="K11" t="n">
+      <c r="L11" t="n">
         <v>15</v>
       </c>
-      <c r="L11" t="n">
+      <c r="M11" t="n">
         <v>11</v>
       </c>
-      <c r="M11" t="n">
+      <c r="N11" t="n">
         <v>28</v>
       </c>
-      <c r="N11" t="n">
+      <c r="O11" t="n">
         <v>5</v>
       </c>
-      <c r="O11" t="n">
-        <v>13</v>
-      </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="Q11" t="n">
+        <v>0</v>
+      </c>
+      <c r="R11" t="n">
         <v>1335.04</v>
       </c>
-      <c r="R11" t="n">
+      <c r="S11" t="n">
         <v>286.72</v>
       </c>
-      <c r="S11" t="n">
-        <v>0</v>
-      </c>
       <c r="T11" t="n">
+        <v>0</v>
+      </c>
+      <c r="U11" t="n">
         <v>286.72</v>
       </c>
-      <c r="U11" t="n">
-        <v>1550</v>
-      </c>
       <c r="V11" t="n">
+        <v>1125</v>
+      </c>
+      <c r="W11" t="n">
         <v>7607744.206532921</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>C-rate</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
+      <c r="A12" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Preco UC</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
         <v>5.78</v>
       </c>
-      <c r="C12" t="n">
+      <c r="D12" t="n">
         <v>5.3</v>
       </c>
-      <c r="D12" t="n">
+      <c r="E12" t="n">
         <v>10</v>
       </c>
-      <c r="E12" t="n">
+      <c r="F12" t="n">
         <v>53</v>
       </c>
-      <c r="F12" t="n">
+      <c r="G12" t="n">
         <v>12.8</v>
       </c>
-      <c r="G12" t="n">
+      <c r="H12" t="n">
         <v>67.84</v>
       </c>
-      <c r="H12" t="n">
-        <v>9.75</v>
-      </c>
       <c r="I12" t="n">
-        <v>51.675</v>
+        <v>13.65</v>
       </c>
       <c r="J12" t="n">
-        <v>2</v>
+        <v>72.345</v>
       </c>
       <c r="K12" t="n">
+        <v>6</v>
+      </c>
+      <c r="L12" t="n">
         <v>15</v>
       </c>
-      <c r="L12" t="n">
+      <c r="M12" t="n">
         <v>11</v>
       </c>
-      <c r="M12" t="n">
-        <v>26</v>
-      </c>
       <c r="N12" t="n">
-        <v>4</v>
+        <v>28</v>
       </c>
       <c r="O12" t="n">
-        <v>26</v>
+        <v>5</v>
       </c>
       <c r="P12" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="Q12" t="n">
-        <v>1404.416</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>212.992</v>
+        <v>1335.04</v>
       </c>
       <c r="S12" t="n">
-        <v>3.2448</v>
+        <v>286.72</v>
       </c>
       <c r="T12" t="n">
-        <v>216.2368</v>
+        <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>1025</v>
+        <v>286.72</v>
       </c>
       <c r="V12" t="n">
-        <v>2601760.656935178</v>
+        <v>1550</v>
+      </c>
+      <c r="W12" t="n">
+        <v>7607744.206532921</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
+      <c r="A13" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="B13" t="inlineStr">
         <is>
           <t>C-rate</t>
         </is>
       </c>
-      <c r="B13" t="n">
+      <c r="C13" t="n">
         <v>5.78</v>
       </c>
-      <c r="C13" t="n">
+      <c r="D13" t="n">
         <v>5.3</v>
       </c>
-      <c r="D13" t="n">
+      <c r="E13" t="n">
         <v>10</v>
       </c>
-      <c r="E13" t="n">
+      <c r="F13" t="n">
         <v>53</v>
       </c>
-      <c r="F13" t="n">
+      <c r="G13" t="n">
         <v>12.8</v>
       </c>
-      <c r="G13" t="n">
+      <c r="H13" t="n">
         <v>67.84</v>
       </c>
-      <c r="H13" t="n">
+      <c r="I13" t="n">
         <v>9.75</v>
       </c>
-      <c r="I13" t="n">
+      <c r="J13" t="n">
         <v>51.675</v>
       </c>
-      <c r="J13" t="n">
-        <v>10</v>
-      </c>
       <c r="K13" t="n">
+        <v>2</v>
+      </c>
+      <c r="L13" t="n">
         <v>15</v>
       </c>
-      <c r="L13" t="n">
+      <c r="M13" t="n">
         <v>11</v>
       </c>
-      <c r="M13" t="n">
-        <v>28</v>
-      </c>
       <c r="N13" t="n">
-        <v>3</v>
+        <v>26</v>
       </c>
       <c r="O13" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="Q13" t="n">
-        <v>801.024</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>172.032</v>
+        <v>1239.68</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>266.24</v>
       </c>
       <c r="T13" t="n">
-        <v>172.032</v>
+        <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>1950</v>
+        <v>266.24</v>
       </c>
       <c r="V13" t="n">
-        <v>7798359.24584867</v>
+        <v>1025</v>
+      </c>
+      <c r="W13" t="n">
+        <v>3012843.172871469</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Nm_b min</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
+      <c r="A14" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>C-rate</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
         <v>5.78</v>
       </c>
-      <c r="C14" t="n">
+      <c r="D14" t="n">
         <v>5.3</v>
       </c>
-      <c r="D14" t="n">
+      <c r="E14" t="n">
         <v>10</v>
       </c>
-      <c r="E14" t="n">
+      <c r="F14" t="n">
         <v>53</v>
       </c>
-      <c r="F14" t="n">
+      <c r="G14" t="n">
         <v>12.8</v>
       </c>
-      <c r="G14" t="n">
+      <c r="H14" t="n">
         <v>67.84</v>
       </c>
-      <c r="H14" t="n">
+      <c r="I14" t="n">
         <v>9.75</v>
       </c>
-      <c r="I14" t="n">
+      <c r="J14" t="n">
         <v>51.675</v>
       </c>
-      <c r="J14" t="n">
-        <v>6</v>
-      </c>
       <c r="K14" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="L14" t="n">
+        <v>15</v>
+      </c>
+      <c r="M14" t="n">
         <v>11</v>
       </c>
-      <c r="M14" t="n">
+      <c r="N14" t="n">
         <v>28</v>
       </c>
-      <c r="N14" t="n">
-        <v>4</v>
-      </c>
       <c r="O14" t="n">
-        <v>24</v>
+        <v>3</v>
       </c>
       <c r="P14" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="Q14" t="n">
-        <v>1258.496</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>229.376</v>
+        <v>801.024</v>
       </c>
       <c r="S14" t="n">
-        <v>1.4976</v>
+        <v>172.032</v>
       </c>
       <c r="T14" t="n">
-        <v>230.8736</v>
+        <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>1425</v>
+        <v>172.032</v>
       </c>
       <c r="V14" t="n">
-        <v>6965234.275311393</v>
+        <v>1950</v>
+      </c>
+      <c r="W14" t="n">
+        <v>7798359.24584867</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
+      <c r="A15" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="B15" t="inlineStr">
         <is>
           <t>Nm_b min</t>
         </is>
       </c>
-      <c r="B15" t="n">
+      <c r="C15" t="n">
         <v>5.78</v>
       </c>
-      <c r="C15" t="n">
+      <c r="D15" t="n">
         <v>5.3</v>
       </c>
-      <c r="D15" t="n">
+      <c r="E15" t="n">
         <v>10</v>
       </c>
-      <c r="E15" t="n">
+      <c r="F15" t="n">
         <v>53</v>
       </c>
-      <c r="F15" t="n">
+      <c r="G15" t="n">
         <v>12.8</v>
       </c>
-      <c r="G15" t="n">
+      <c r="H15" t="n">
         <v>67.84</v>
       </c>
-      <c r="H15" t="n">
+      <c r="I15" t="n">
         <v>9.75</v>
       </c>
-      <c r="I15" t="n">
+      <c r="J15" t="n">
         <v>51.675</v>
       </c>
-      <c r="J15" t="n">
+      <c r="K15" t="n">
         <v>6</v>
       </c>
-      <c r="K15" t="n">
-        <v>22</v>
-      </c>
       <c r="L15" t="n">
+        <v>8</v>
+      </c>
+      <c r="M15" t="n">
         <v>11</v>
       </c>
-      <c r="M15" t="n">
+      <c r="N15" t="n">
         <v>28</v>
       </c>
-      <c r="N15" t="n">
+      <c r="O15" t="n">
         <v>4</v>
       </c>
-      <c r="O15" t="n">
-        <v>24</v>
-      </c>
       <c r="P15" t="n">
+        <v>21</v>
+      </c>
+      <c r="Q15" t="n">
         <v>1</v>
       </c>
-      <c r="Q15" t="n">
-        <v>1258.496</v>
-      </c>
       <c r="R15" t="n">
+        <v>1234.688</v>
+      </c>
+      <c r="S15" t="n">
         <v>229.376</v>
       </c>
-      <c r="S15" t="n">
-        <v>1.4976</v>
-      </c>
       <c r="T15" t="n">
-        <v>230.8736</v>
+        <v>1.3104</v>
       </c>
       <c r="U15" t="n">
-        <v>1425</v>
+        <v>230.6864</v>
       </c>
       <c r="V15" t="n">
-        <v>6965234.275311393</v>
+        <v>1375</v>
+      </c>
+      <c r="W15" t="n">
+        <v>7006170.727263453</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Nm_uc min</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
+      <c r="A16" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Nm_b min</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
         <v>5.78</v>
       </c>
-      <c r="C16" t="n">
+      <c r="D16" t="n">
         <v>5.3</v>
       </c>
-      <c r="D16" t="n">
+      <c r="E16" t="n">
         <v>10</v>
       </c>
-      <c r="E16" t="n">
+      <c r="F16" t="n">
         <v>53</v>
       </c>
-      <c r="F16" t="n">
+      <c r="G16" t="n">
         <v>12.8</v>
       </c>
-      <c r="G16" t="n">
+      <c r="H16" t="n">
         <v>67.84</v>
       </c>
-      <c r="H16" t="n">
+      <c r="I16" t="n">
         <v>9.75</v>
       </c>
-      <c r="I16" t="n">
+      <c r="J16" t="n">
         <v>51.675</v>
       </c>
-      <c r="J16" t="n">
+      <c r="K16" t="n">
         <v>6</v>
       </c>
-      <c r="K16" t="n">
-        <v>15</v>
-      </c>
       <c r="L16" t="n">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="M16" t="n">
+        <v>11</v>
+      </c>
+      <c r="N16" t="n">
         <v>28</v>
       </c>
-      <c r="N16" t="n">
+      <c r="O16" t="n">
         <v>4</v>
       </c>
-      <c r="O16" t="n">
-        <v>24</v>
-      </c>
       <c r="P16" t="n">
+        <v>21</v>
+      </c>
+      <c r="Q16" t="n">
         <v>1</v>
       </c>
-      <c r="Q16" t="n">
-        <v>1258.496</v>
-      </c>
       <c r="R16" t="n">
+        <v>1234.688</v>
+      </c>
+      <c r="S16" t="n">
         <v>229.376</v>
       </c>
-      <c r="S16" t="n">
-        <v>1.4976</v>
-      </c>
       <c r="T16" t="n">
-        <v>230.8736</v>
+        <v>1.3104</v>
       </c>
       <c r="U16" t="n">
-        <v>1425</v>
+        <v>230.6864</v>
       </c>
       <c r="V16" t="n">
-        <v>6965234.275311393</v>
+        <v>1375</v>
+      </c>
+      <c r="W16" t="n">
+        <v>7006170.727263453</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
+      <c r="A17" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="B17" t="inlineStr">
         <is>
           <t>Nm_uc min</t>
         </is>
       </c>
-      <c r="B17" t="n">
+      <c r="C17" t="n">
         <v>5.78</v>
       </c>
-      <c r="C17" t="n">
+      <c r="D17" t="n">
         <v>5.3</v>
       </c>
-      <c r="D17" t="n">
+      <c r="E17" t="n">
         <v>10</v>
       </c>
-      <c r="E17" t="n">
+      <c r="F17" t="n">
         <v>53</v>
       </c>
-      <c r="F17" t="n">
+      <c r="G17" t="n">
         <v>12.8</v>
       </c>
-      <c r="G17" t="n">
+      <c r="H17" t="n">
         <v>67.84</v>
       </c>
-      <c r="H17" t="n">
+      <c r="I17" t="n">
         <v>9.75</v>
       </c>
-      <c r="I17" t="n">
+      <c r="J17" t="n">
         <v>51.675</v>
       </c>
-      <c r="J17" t="n">
+      <c r="K17" t="n">
         <v>6</v>
       </c>
-      <c r="K17" t="n">
+      <c r="L17" t="n">
         <v>15</v>
       </c>
-      <c r="L17" t="n">
-        <v>18</v>
-      </c>
       <c r="M17" t="n">
+        <v>6</v>
+      </c>
+      <c r="N17" t="n">
         <v>28</v>
       </c>
-      <c r="N17" t="n">
+      <c r="O17" t="n">
         <v>4</v>
       </c>
-      <c r="O17" t="n">
-        <v>24</v>
-      </c>
       <c r="P17" t="n">
+        <v>21</v>
+      </c>
+      <c r="Q17" t="n">
         <v>1</v>
       </c>
-      <c r="Q17" t="n">
-        <v>1258.496</v>
-      </c>
       <c r="R17" t="n">
+        <v>1234.688</v>
+      </c>
+      <c r="S17" t="n">
         <v>229.376</v>
       </c>
-      <c r="S17" t="n">
-        <v>1.4976</v>
-      </c>
       <c r="T17" t="n">
-        <v>230.8736</v>
+        <v>1.3104</v>
       </c>
       <c r="U17" t="n">
-        <v>1425</v>
+        <v>230.6864</v>
       </c>
       <c r="V17" t="n">
-        <v>6965234.275311393</v>
+        <v>1375</v>
+      </c>
+      <c r="W17" t="n">
+        <v>7006170.727263453</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Caso base</t>
-        </is>
-      </c>
-      <c r="B18" t="n">
+      <c r="A18" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Nm_uc min</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
         <v>5.78</v>
       </c>
-      <c r="C18" t="n">
+      <c r="D18" t="n">
         <v>5.3</v>
       </c>
-      <c r="D18" t="n">
+      <c r="E18" t="n">
         <v>10</v>
       </c>
-      <c r="E18" t="n">
+      <c r="F18" t="n">
         <v>53</v>
       </c>
-      <c r="F18" t="n">
+      <c r="G18" t="n">
         <v>12.8</v>
       </c>
-      <c r="G18" t="n">
+      <c r="H18" t="n">
         <v>67.84</v>
       </c>
-      <c r="H18" t="n">
+      <c r="I18" t="n">
         <v>9.75</v>
       </c>
-      <c r="I18" t="n">
+      <c r="J18" t="n">
         <v>51.675</v>
       </c>
-      <c r="J18" t="n">
+      <c r="K18" t="n">
         <v>6</v>
       </c>
-      <c r="K18" t="n">
+      <c r="L18" t="n">
         <v>15</v>
       </c>
-      <c r="L18" t="n">
-        <v>11</v>
-      </c>
       <c r="M18" t="n">
+        <v>18</v>
+      </c>
+      <c r="N18" t="n">
         <v>28</v>
       </c>
-      <c r="N18" t="n">
+      <c r="O18" t="n">
         <v>4</v>
       </c>
-      <c r="O18" t="n">
+      <c r="P18" t="n">
         <v>21</v>
       </c>
-      <c r="P18" t="n">
+      <c r="Q18" t="n">
         <v>1</v>
       </c>
-      <c r="Q18" t="n">
+      <c r="R18" t="n">
         <v>1234.688</v>
       </c>
-      <c r="R18" t="n">
+      <c r="S18" t="n">
         <v>229.376</v>
       </c>
-      <c r="S18" t="n">
+      <c r="T18" t="n">
         <v>1.3104</v>
       </c>
-      <c r="T18" t="n">
+      <c r="U18" t="n">
         <v>230.6864</v>
       </c>
-      <c r="U18" t="n">
+      <c r="V18" t="n">
         <v>1375</v>
       </c>
-      <c r="V18" t="n">
+      <c r="W18" t="n">
         <v>7006170.727263453</v>
       </c>
     </row>
